--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7753DB-BC7C-454B-81B5-03CA2E15C846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB56F5ED-9FC7-4E7D-86B8-812EEFFBACAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>รับรองความถูกต้อง</t>
-  </si>
-  <si>
-    <t>(นายเจษฎากร  ปานสุวรรณ)</t>
   </si>
   <si>
     <t>(นางสาวอัญญารัตน์ แสงจันทร์)</t>
@@ -280,6 +277,9 @@
   </si>
   <si>
     <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
+  </si>
+  <si>
+    <t>(NAME)</t>
   </si>
 </sst>
 </file>
@@ -717,100 +717,43 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -852,28 +795,85 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1999,46 +1999,46 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="84" t="s">
+      <c r="J1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="87" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="88"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="89"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="44"/>
       <c r="L3" s="10">
         <v>86</v>
       </c>
@@ -2047,50 +2047,50 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="90" t="s">
+      <c r="A4" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="91"/>
+      <c r="M4" s="47"/>
     </row>
     <row r="5" spans="1:13" ht="20.399999999999999">
       <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="46"/>
+      <c r="B5" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="51"/>
       <c r="D5" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="52"/>
+      <c r="J5" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="H5" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="17" t="s">
-        <v>54</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>4</v>
@@ -2103,13 +2103,13 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="53" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="55" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="20" t="s">
@@ -2133,26 +2133,26 @@
       <c r="J6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="76" t="s">
+      <c r="K6" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="77"/>
-      <c r="M6" s="78"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="59"/>
     </row>
     <row r="7" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A7" s="73"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="79" t="s">
+      <c r="C7" s="56"/>
+      <c r="D7" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="79" t="s">
+      <c r="E7" s="61"/>
+      <c r="F7" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="80"/>
+      <c r="G7" s="61"/>
       <c r="H7" s="21" t="s">
         <v>21</v>
       </c>
@@ -2162,11 +2162,11 @@
       <c r="J7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="81" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="82"/>
-      <c r="M7" s="83"/>
+      <c r="K7" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="63"/>
+      <c r="M7" s="64"/>
     </row>
     <row r="8" spans="1:13" ht="18" customHeight="1">
       <c r="A8" s="25">
@@ -2181,9 +2181,9 @@
       <c r="H8" s="29"/>
       <c r="I8" s="30"/>
       <c r="J8" s="31"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="57"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="67"/>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1">
       <c r="A9" s="26">
@@ -2213,7 +2213,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" s="28" t="s">
         <v>27</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I10" s="30"/>
       <c r="J10" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K10" s="68"/>
       <c r="L10" s="69"/>
@@ -2265,9 +2265,9 @@
       <c r="H12" s="29"/>
       <c r="I12" s="30"/>
       <c r="J12" s="31"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="61"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="73"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1">
       <c r="A13" s="26">
@@ -2282,9 +2282,9 @@
       <c r="H13" s="29"/>
       <c r="I13" s="30"/>
       <c r="J13" s="31"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="52"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="50"/>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
       <c r="A14" s="26">
@@ -2316,9 +2316,9 @@
       <c r="H15" s="29"/>
       <c r="I15" s="30"/>
       <c r="J15" s="31"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="61"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="73"/>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1">
       <c r="A16" s="26">
@@ -2333,9 +2333,9 @@
       <c r="H16" s="29"/>
       <c r="I16" s="30"/>
       <c r="J16" s="31"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="61"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="73"/>
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1">
       <c r="A17" s="26">
@@ -2350,9 +2350,9 @@
       <c r="H17" s="29"/>
       <c r="I17" s="30"/>
       <c r="J17" s="31"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="61"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="73"/>
     </row>
     <row r="18" spans="1:13" ht="18" customHeight="1">
       <c r="A18" s="32">
@@ -2379,9 +2379,9 @@
       <c r="J18" s="31">
         <v>688</v>
       </c>
-      <c r="K18" s="53"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="61"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="73"/>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1">
       <c r="A19" s="26">
@@ -2408,9 +2408,9 @@
       <c r="J19" s="31">
         <v>688</v>
       </c>
-      <c r="K19" s="50"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="52"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="50"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1">
       <c r="A20" s="32">
@@ -2466,9 +2466,9 @@
       <c r="J21" s="31">
         <v>688</v>
       </c>
-      <c r="K21" s="53"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="61"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="73"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1">
       <c r="A22" s="32">
@@ -2495,9 +2495,9 @@
       <c r="J22" s="31">
         <v>688</v>
       </c>
-      <c r="K22" s="53"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="61"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="73"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1">
       <c r="A23" s="26">
@@ -2512,9 +2512,9 @@
       <c r="H23" s="29"/>
       <c r="I23" s="30"/>
       <c r="J23" s="31"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="61"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="73"/>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1">
       <c r="A24" s="32">
@@ -2529,9 +2529,9 @@
       <c r="H24" s="29"/>
       <c r="I24" s="30"/>
       <c r="J24" s="31"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="61"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="73"/>
     </row>
     <row r="25" spans="1:13" ht="18" customHeight="1">
       <c r="A25" s="26">
@@ -2546,9 +2546,9 @@
       <c r="H25" s="29"/>
       <c r="I25" s="30"/>
       <c r="J25" s="31"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="67"/>
+      <c r="K25" s="74"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:13" ht="18" customHeight="1">
       <c r="A26" s="32">
@@ -2563,9 +2563,9 @@
       <c r="H26" s="29"/>
       <c r="I26" s="30"/>
       <c r="J26" s="31"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="61"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="73"/>
     </row>
     <row r="27" spans="1:13" ht="18" customHeight="1">
       <c r="A27" s="26">
@@ -2580,11 +2580,11 @@
       <c r="H27" s="29"/>
       <c r="I27" s="30"/>
       <c r="J27" s="31"/>
-      <c r="K27" s="53" t="s">
+      <c r="K27" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="54"/>
-      <c r="M27" s="61"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="73"/>
     </row>
     <row r="28" spans="1:13" ht="18" customHeight="1">
       <c r="A28" s="32">
@@ -2599,11 +2599,11 @@
       <c r="H28" s="29"/>
       <c r="I28" s="30"/>
       <c r="J28" s="31"/>
-      <c r="K28" s="53" t="s">
+      <c r="K28" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="L28" s="54"/>
-      <c r="M28" s="61"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="73"/>
     </row>
     <row r="29" spans="1:13" ht="18" customHeight="1">
       <c r="A29" s="26">
@@ -2618,11 +2618,11 @@
       <c r="H29" s="29"/>
       <c r="I29" s="30"/>
       <c r="J29" s="31"/>
-      <c r="K29" s="65" t="s">
-        <v>56</v>
-      </c>
-      <c r="L29" s="66"/>
-      <c r="M29" s="67"/>
+      <c r="K29" s="74" t="s">
+        <v>55</v>
+      </c>
+      <c r="L29" s="75"/>
+      <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:13" ht="18" customHeight="1">
       <c r="A30" s="32">
@@ -2637,9 +2637,9 @@
       <c r="H30" s="29"/>
       <c r="I30" s="30"/>
       <c r="J30" s="31"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="54"/>
-      <c r="M30" s="61"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="73"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1">
       <c r="A31" s="26">
@@ -2654,9 +2654,9 @@
       <c r="H31" s="29"/>
       <c r="I31" s="30"/>
       <c r="J31" s="31"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="61"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="73"/>
     </row>
     <row r="32" spans="1:13" ht="18" customHeight="1">
       <c r="A32" s="32">
@@ -2671,9 +2671,9 @@
       <c r="H32" s="29"/>
       <c r="I32" s="30"/>
       <c r="J32" s="31"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="54"/>
-      <c r="M32" s="61"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="73"/>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1">
       <c r="A33" s="26">
@@ -2688,9 +2688,9 @@
       <c r="H33" s="29"/>
       <c r="I33" s="30"/>
       <c r="J33" s="31"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="61"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="73"/>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1">
       <c r="A34" s="32">
@@ -2705,9 +2705,9 @@
       <c r="H34" s="29"/>
       <c r="I34" s="30"/>
       <c r="J34" s="31"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="61"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="73"/>
     </row>
     <row r="35" spans="1:13" ht="18" customHeight="1">
       <c r="A35" s="26">
@@ -2722,9 +2722,9 @@
       <c r="H35" s="29"/>
       <c r="I35" s="30"/>
       <c r="J35" s="31"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="52"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="50"/>
     </row>
     <row r="36" spans="1:13" ht="18" customHeight="1">
       <c r="A36" s="32">
@@ -2739,9 +2739,9 @@
       <c r="H36" s="29"/>
       <c r="I36" s="30"/>
       <c r="J36" s="31"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="52"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="50"/>
     </row>
     <row r="37" spans="1:13" ht="18" customHeight="1">
       <c r="A37" s="26">
@@ -2756,9 +2756,9 @@
       <c r="H37" s="29"/>
       <c r="I37" s="30"/>
       <c r="J37" s="31"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="61"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="72"/>
+      <c r="M37" s="73"/>
     </row>
     <row r="38" spans="1:13" ht="18" customHeight="1">
       <c r="A38" s="32"/>
@@ -2771,22 +2771,22 @@
       <c r="H38" s="29"/>
       <c r="I38" s="30"/>
       <c r="J38" s="31"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="54"/>
-      <c r="M38" s="61"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="73"/>
     </row>
     <row r="39" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="48"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="49" t="s">
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
       <c r="H39" s="28" t="s">
         <v>36</v>
       </c>
@@ -2795,67 +2795,67 @@
         <f>(H39*$L$5)+(I39*$L$3)</f>
         <v>4128</v>
       </c>
-      <c r="K39" s="50" t="s">
+      <c r="K39" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="L39" s="51"/>
-      <c r="M39" s="52"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="50"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
       <c r="H40" s="28"/>
       <c r="I40" s="26"/>
       <c r="J40" s="36">
         <f>H40*L5</f>
         <v>0</v>
       </c>
-      <c r="K40" s="62" t="s">
-        <v>61</v>
-      </c>
-      <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="K40" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="84"/>
+      <c r="M40" s="85"/>
     </row>
     <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
       <c r="H41" s="35"/>
       <c r="I41" s="26"/>
       <c r="J41" s="36">
         <f>I41*L3</f>
         <v>0</v>
       </c>
-      <c r="K41" s="50" t="s">
+      <c r="K41" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="51"/>
-      <c r="M41" s="52"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="50"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="53" t="str">
+      <c r="A42" s="71" t="str">
         <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
         <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
       <c r="H42" s="28" t="s">
         <v>36</v>
       </c>
@@ -2864,110 +2864,110 @@
         <f>SUM(J39:J41)</f>
         <v>4128</v>
       </c>
-      <c r="K42" s="55" t="s">
+      <c r="K42" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="L42" s="56"/>
-      <c r="M42" s="57"/>
+      <c r="L42" s="66"/>
+      <c r="M42" s="67"/>
     </row>
     <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A43" s="58" t="s">
+      <c r="A43" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="58" t="s">
+      <c r="B43" s="78"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="79"/>
+      <c r="E43" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="58" t="s">
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="L43" s="59"/>
-      <c r="M43" s="60"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="79"/>
     </row>
     <row r="44" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A44" s="39"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="41"/>
+      <c r="A44" s="86"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="45"/>
+      <c r="D44" s="80"/>
+      <c r="E44" s="86"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="80"/>
+      <c r="K44" s="86"/>
+      <c r="L44" s="45"/>
+      <c r="M44" s="80"/>
     </row>
     <row r="45" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A45" s="39" t="s">
+      <c r="A45" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="45"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="80"/>
+      <c r="E45" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="40"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="39" t="s">
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="80"/>
+      <c r="K45" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="39" t="s">
+      <c r="L45" s="45"/>
+      <c r="M45" s="80"/>
+    </row>
+    <row r="46" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A46" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="L45" s="40"/>
-      <c r="M45" s="41"/>
-    </row>
-    <row r="46" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A46" s="39" t="s">
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="80"/>
+      <c r="E46" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="39" t="s">
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="80"/>
+      <c r="K46" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="42" t="s">
+      <c r="L46" s="88"/>
+      <c r="M46" s="89"/>
+    </row>
+    <row r="47" spans="1:13" ht="21" customHeight="1">
+      <c r="A47" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="51"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="91"/>
+      <c r="E47" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="L46" s="43"/>
-      <c r="M46" s="44"/>
-    </row>
-    <row r="47" spans="1:13" ht="21" customHeight="1">
-      <c r="A47" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="45" t="s">
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="L47" s="46"/>
-      <c r="M47" s="47"/>
+      <c r="L47" s="51"/>
+      <c r="M47" s="91"/>
     </row>
     <row r="48" spans="1:13" ht="18">
       <c r="A48" s="4"/>
@@ -3046,50 +3046,18 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="K45:M45"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="E43:J43"/>
     <mergeCell ref="K43:M43"/>
@@ -3105,18 +3073,50 @@
     <mergeCell ref="K41:M41"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="K42:M42"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="L4:M4"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB56F5ED-9FC7-4E7D-86B8-812EEFFBACAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E4A0A5-927E-4D94-ACF0-E1FB75DE2889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>เลขที่คำขอระบบ HRIS................</t>
   </si>
@@ -277,9 +277,6 @@
   </si>
   <si>
     <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
-  </si>
-  <si>
-    <t>(NAME)</t>
   </si>
 </sst>
 </file>
@@ -717,31 +714,55 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -753,7 +774,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -795,85 +849,28 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1999,46 +1996,46 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="42" t="s">
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="43"/>
+      <c r="M2" s="88"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="44"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="89"/>
       <c r="L3" s="10">
         <v>86</v>
       </c>
@@ -2047,32 +2044,32 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="46" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="47"/>
+      <c r="M4" s="91"/>
     </row>
     <row r="5" spans="1:13" ht="20.399999999999999">
       <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="51"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="13" t="s">
         <v>7</v>
       </c>
@@ -2085,10 +2082,10 @@
       <c r="G5" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="52"/>
+      <c r="I5" s="71"/>
       <c r="J5" s="17" t="s">
         <v>53</v>
       </c>
@@ -2103,13 +2100,13 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="72" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="74" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="20" t="s">
@@ -2133,26 +2130,26 @@
       <c r="J6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="57" t="s">
+      <c r="K6" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="58"/>
-      <c r="M6" s="59"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="78"/>
     </row>
     <row r="7" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A7" s="54"/>
+      <c r="A7" s="73"/>
       <c r="B7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="60" t="s">
+      <c r="C7" s="75"/>
+      <c r="D7" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="60" t="s">
+      <c r="E7" s="80"/>
+      <c r="F7" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="61"/>
+      <c r="G7" s="80"/>
       <c r="H7" s="21" t="s">
         <v>21</v>
       </c>
@@ -2162,11 +2159,11 @@
       <c r="J7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="62" t="s">
+      <c r="K7" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="63"/>
-      <c r="M7" s="64"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="83"/>
     </row>
     <row r="8" spans="1:13" ht="18" customHeight="1">
       <c r="A8" s="25">
@@ -2181,9 +2178,9 @@
       <c r="H8" s="29"/>
       <c r="I8" s="30"/>
       <c r="J8" s="31"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="67"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1">
       <c r="A9" s="26">
@@ -2265,9 +2262,9 @@
       <c r="H12" s="29"/>
       <c r="I12" s="30"/>
       <c r="J12" s="31"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="53"/>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1">
       <c r="A13" s="26">
@@ -2282,9 +2279,9 @@
       <c r="H13" s="29"/>
       <c r="I13" s="30"/>
       <c r="J13" s="31"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="50"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="58"/>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
       <c r="A14" s="26">
@@ -2316,9 +2313,9 @@
       <c r="H15" s="29"/>
       <c r="I15" s="30"/>
       <c r="J15" s="31"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="73"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="53"/>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1">
       <c r="A16" s="26">
@@ -2333,9 +2330,9 @@
       <c r="H16" s="29"/>
       <c r="I16" s="30"/>
       <c r="J16" s="31"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="73"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="53"/>
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1">
       <c r="A17" s="26">
@@ -2350,9 +2347,9 @@
       <c r="H17" s="29"/>
       <c r="I17" s="30"/>
       <c r="J17" s="31"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="73"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="53"/>
     </row>
     <row r="18" spans="1:13" ht="18" customHeight="1">
       <c r="A18" s="32">
@@ -2379,9 +2376,9 @@
       <c r="J18" s="31">
         <v>688</v>
       </c>
-      <c r="K18" s="71"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="73"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="53"/>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1">
       <c r="A19" s="26">
@@ -2408,9 +2405,9 @@
       <c r="J19" s="31">
         <v>688</v>
       </c>
-      <c r="K19" s="48"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="50"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1">
       <c r="A20" s="32">
@@ -2466,9 +2463,9 @@
       <c r="J21" s="31">
         <v>688</v>
       </c>
-      <c r="K21" s="71"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="73"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="53"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1">
       <c r="A22" s="32">
@@ -2495,9 +2492,9 @@
       <c r="J22" s="31">
         <v>688</v>
       </c>
-      <c r="K22" s="71"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="73"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="53"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1">
       <c r="A23" s="26">
@@ -2512,9 +2509,9 @@
       <c r="H23" s="29"/>
       <c r="I23" s="30"/>
       <c r="J23" s="31"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="73"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1">
       <c r="A24" s="32">
@@ -2529,9 +2526,9 @@
       <c r="H24" s="29"/>
       <c r="I24" s="30"/>
       <c r="J24" s="31"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="73"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="53"/>
     </row>
     <row r="25" spans="1:13" ht="18" customHeight="1">
       <c r="A25" s="26">
@@ -2546,9 +2543,9 @@
       <c r="H25" s="29"/>
       <c r="I25" s="30"/>
       <c r="J25" s="31"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="76"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="67"/>
     </row>
     <row r="26" spans="1:13" ht="18" customHeight="1">
       <c r="A26" s="32">
@@ -2563,9 +2560,9 @@
       <c r="H26" s="29"/>
       <c r="I26" s="30"/>
       <c r="J26" s="31"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="73"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="53"/>
     </row>
     <row r="27" spans="1:13" ht="18" customHeight="1">
       <c r="A27" s="26">
@@ -2580,11 +2577,11 @@
       <c r="H27" s="29"/>
       <c r="I27" s="30"/>
       <c r="J27" s="31"/>
-      <c r="K27" s="71" t="s">
+      <c r="K27" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="72"/>
-      <c r="M27" s="73"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
     </row>
     <row r="28" spans="1:13" ht="18" customHeight="1">
       <c r="A28" s="32">
@@ -2599,11 +2596,11 @@
       <c r="H28" s="29"/>
       <c r="I28" s="30"/>
       <c r="J28" s="31"/>
-      <c r="K28" s="71" t="s">
+      <c r="K28" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="L28" s="72"/>
-      <c r="M28" s="73"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="53"/>
     </row>
     <row r="29" spans="1:13" ht="18" customHeight="1">
       <c r="A29" s="26">
@@ -2618,11 +2615,11 @@
       <c r="H29" s="29"/>
       <c r="I29" s="30"/>
       <c r="J29" s="31"/>
-      <c r="K29" s="74" t="s">
+      <c r="K29" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="L29" s="75"/>
-      <c r="M29" s="76"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="67"/>
     </row>
     <row r="30" spans="1:13" ht="18" customHeight="1">
       <c r="A30" s="32">
@@ -2637,9 +2634,9 @@
       <c r="H30" s="29"/>
       <c r="I30" s="30"/>
       <c r="J30" s="31"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="73"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="53"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1">
       <c r="A31" s="26">
@@ -2654,9 +2651,9 @@
       <c r="H31" s="29"/>
       <c r="I31" s="30"/>
       <c r="J31" s="31"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="73"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="53"/>
     </row>
     <row r="32" spans="1:13" ht="18" customHeight="1">
       <c r="A32" s="32">
@@ -2671,9 +2668,9 @@
       <c r="H32" s="29"/>
       <c r="I32" s="30"/>
       <c r="J32" s="31"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="73"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="53"/>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1">
       <c r="A33" s="26">
@@ -2688,9 +2685,9 @@
       <c r="H33" s="29"/>
       <c r="I33" s="30"/>
       <c r="J33" s="31"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="72"/>
-      <c r="M33" s="73"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="53"/>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1">
       <c r="A34" s="32">
@@ -2705,9 +2702,9 @@
       <c r="H34" s="29"/>
       <c r="I34" s="30"/>
       <c r="J34" s="31"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="72"/>
-      <c r="M34" s="73"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="53"/>
     </row>
     <row r="35" spans="1:13" ht="18" customHeight="1">
       <c r="A35" s="26">
@@ -2722,9 +2719,9 @@
       <c r="H35" s="29"/>
       <c r="I35" s="30"/>
       <c r="J35" s="31"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="50"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="58"/>
     </row>
     <row r="36" spans="1:13" ht="18" customHeight="1">
       <c r="A36" s="32">
@@ -2739,9 +2736,9 @@
       <c r="H36" s="29"/>
       <c r="I36" s="30"/>
       <c r="J36" s="31"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="50"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="58"/>
     </row>
     <row r="37" spans="1:13" ht="18" customHeight="1">
       <c r="A37" s="26">
@@ -2756,9 +2753,9 @@
       <c r="H37" s="29"/>
       <c r="I37" s="30"/>
       <c r="J37" s="31"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="72"/>
-      <c r="M37" s="73"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="53"/>
     </row>
     <row r="38" spans="1:13" ht="18" customHeight="1">
       <c r="A38" s="32"/>
@@ -2771,22 +2768,22 @@
       <c r="H38" s="29"/>
       <c r="I38" s="30"/>
       <c r="J38" s="31"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="72"/>
-      <c r="M38" s="73"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="53"/>
     </row>
     <row r="39" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A39" s="81" t="s">
+      <c r="A39" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="81"/>
-      <c r="C39" s="81"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="82" t="s">
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="82"/>
-      <c r="G39" s="82"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
       <c r="H39" s="28" t="s">
         <v>36</v>
       </c>
@@ -2795,67 +2792,67 @@
         <f>(H39*$L$5)+(I39*$L$3)</f>
         <v>4128</v>
       </c>
-      <c r="K39" s="48" t="s">
+      <c r="K39" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="L39" s="49"/>
-      <c r="M39" s="50"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="58"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="81" t="s">
+      <c r="A40" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
       <c r="H40" s="28"/>
       <c r="I40" s="26"/>
       <c r="J40" s="36">
         <f>H40*L5</f>
         <v>0</v>
       </c>
-      <c r="K40" s="83" t="s">
+      <c r="K40" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="L40" s="84"/>
-      <c r="M40" s="85"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="61"/>
     </row>
     <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A41" s="81" t="s">
+      <c r="A41" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="81"/>
-      <c r="C41" s="81"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="82"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
       <c r="H41" s="35"/>
       <c r="I41" s="26"/>
       <c r="J41" s="36">
         <f>I41*L3</f>
         <v>0</v>
       </c>
-      <c r="K41" s="48" t="s">
+      <c r="K41" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="49"/>
-      <c r="M41" s="50"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="58"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="71" t="str">
+      <c r="A42" s="51" t="str">
         <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
         <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
       <c r="H42" s="28" t="s">
         <v>36</v>
       </c>
@@ -2864,110 +2861,110 @@
         <f>SUM(J39:J41)</f>
         <v>4128</v>
       </c>
-      <c r="K42" s="65" t="s">
+      <c r="K42" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="L42" s="66"/>
-      <c r="M42" s="67"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="64"/>
     </row>
     <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A43" s="77" t="s">
+      <c r="A43" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="78"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="77" t="s">
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="77" t="s">
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="41"/>
+      <c r="K43" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="L43" s="78"/>
-      <c r="M43" s="79"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="50"/>
     </row>
     <row r="44" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A44" s="86"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="80"/>
-      <c r="E44" s="86"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="80"/>
-      <c r="K44" s="86"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="80"/>
+      <c r="A44" s="39"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="40"/>
+      <c r="M44" s="41"/>
     </row>
     <row r="45" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A45" s="86" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="80"/>
-      <c r="E45" s="86" t="s">
+      <c r="A45" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="80"/>
-      <c r="K45" s="86" t="s">
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="L45" s="45"/>
-      <c r="M45" s="80"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="41"/>
     </row>
     <row r="46" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A46" s="86" t="s">
+      <c r="A46" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="80"/>
-      <c r="E46" s="86" t="s">
+      <c r="B46" s="40"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="80"/>
-      <c r="K46" s="87" t="s">
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="L46" s="88"/>
-      <c r="M46" s="89"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="44"/>
     </row>
     <row r="47" spans="1:13" ht="21" customHeight="1">
-      <c r="A47" s="90" t="s">
+      <c r="A47" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="90" t="s">
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="51"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="91"/>
-      <c r="K47" s="90" t="s">
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="47"/>
+      <c r="K47" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="L47" s="51"/>
-      <c r="M47" s="91"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="47"/>
     </row>
     <row r="48" spans="1:13" ht="18">
       <c r="A48" s="4"/>
@@ -3046,18 +3043,50 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="E43:J43"/>
     <mergeCell ref="K43:M43"/>
@@ -3073,50 +3102,18 @@
     <mergeCell ref="K41:M41"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="K42:M42"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="K47:M47"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E4A0A5-927E-4D94-ACF0-E1FB75DE2889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5770A49-0F33-470D-BD51-FA795394EC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
   <si>
     <t>เลขที่คำขอระบบ HRIS................</t>
   </si>
@@ -168,9 +168,6 @@
     <t>(นางสาวอัญญารัตน์ แสงจันทร์)</t>
   </si>
   <si>
-    <t>(นายปฐม  ชุมวงศ์)</t>
-  </si>
-  <si>
     <t>ผู้เบิก</t>
   </si>
   <si>
@@ -196,6 +193,37 @@
   </si>
   <si>
     <t>[3]</t>
+  </si>
+  <si>
+    <t>[14]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ปฏิบัติตามคำสั่งฯ เลขที่ รฟ.ดร. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="TH Sarabun New"/>
+        <family val="2"/>
+      </rPr>
+      <t>[7] ลว. [8]</t>
+    </r>
+  </si>
+  <si>
+    <t>[SHIFT_1]</t>
+  </si>
+  <si>
+    <t>[MONEY]</t>
+  </si>
+  <si>
+    <t>วันที่ [14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
+  </si>
+  <si>
+    <t>[1_2]</t>
   </si>
   <si>
     <r>
@@ -213,7 +241,24 @@
         <rFont val="TH Sarabun New"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">         [13]              </t>
+      <t xml:space="preserve">         </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="TH Sarabun New"/>
+        <family val="2"/>
+      </rPr>
+      <t>[13]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="TH Sarabun New"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">              </t>
     </r>
     <r>
       <rPr>
@@ -251,32 +296,7 @@
     </r>
   </si>
   <si>
-    <t>[14]</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ปฏิบัติตามคำสั่งฯ เลขที่ รฟ.ดร. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="TH Sarabun New"/>
-        <family val="2"/>
-      </rPr>
-      <t>[7] ลว. [8]</t>
-    </r>
-  </si>
-  <si>
-    <t>[SHIFT_1]</t>
-  </si>
-  <si>
-    <t>[MONEY]</t>
-  </si>
-  <si>
-    <t>วันที่ [14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
+    <t>(นายปฐม  ชุมวงค์)</t>
   </si>
 </sst>
 </file>
@@ -289,7 +309,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -392,6 +412,25 @@
       <name val="TH Sarabun New"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <name val="TH Sarabun New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="TH Sarabun New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u val="singleAccounting"/>
+      <sz val="12"/>
+      <name val="TH Sarabun New"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -598,7 +637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -633,9 +672,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -651,9 +687,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -714,6 +747,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,7 +867,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -849,9 +906,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -872,6 +926,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1214,7 +1280,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -1996,46 +2062,46 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="84" t="s">
+      <c r="J1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="87" t="s">
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="88"/>
+      <c r="M2" s="93"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="89"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="94"/>
       <c r="L3" s="10">
         <v>86</v>
       </c>
@@ -2044,942 +2110,944 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="95" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="96"/>
+    </row>
+    <row r="5" spans="1:13" ht="20.399999999999999">
+      <c r="A5" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="97" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="46"/>
+      <c r="D5" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="98" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="99" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="77"/>
+      <c r="J5" s="100" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="44">
+        <v>688</v>
+      </c>
+      <c r="M5" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20.399999999999999">
+      <c r="A6" s="39"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="41"/>
+    </row>
+    <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1">
+      <c r="A7" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="83"/>
+      <c r="M7" s="84"/>
+    </row>
+    <row r="8" spans="1:13" ht="25.5" customHeight="1">
+      <c r="A8" s="79"/>
+      <c r="B8" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="81"/>
+      <c r="D8" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="86"/>
+      <c r="F8" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="86"/>
+      <c r="H8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="90" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="91"/>
-    </row>
-    <row r="5" spans="1:13" ht="20.399999999999999">
-      <c r="A5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="18">
-        <v>688</v>
-      </c>
-      <c r="M5" s="38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="72" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="76" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="77"/>
-      <c r="M6" s="78"/>
-    </row>
-    <row r="7" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A7" s="73"/>
-      <c r="B7" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="82"/>
-      <c r="M7" s="83"/>
-    </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1">
-      <c r="A8" s="25">
+      <c r="L8" s="88"/>
+      <c r="M8" s="89"/>
+    </row>
+    <row r="9" spans="1:13" ht="18" customHeight="1">
+      <c r="A9" s="23">
         <v>1</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="64"/>
-    </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1">
-      <c r="A9" s="26">
-        <v>2</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="29"/>
       <c r="K9" s="68"/>
       <c r="L9" s="69"/>
       <c r="M9" s="70"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="32">
+      <c r="A10" s="24">
+        <v>2</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="76"/>
+    </row>
+    <row r="11" spans="1:13" ht="18" customHeight="1">
+      <c r="A11" s="30">
         <v>3</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B11" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C11" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="28" t="s">
+      <c r="D11" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F11" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G11" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H11" s="27">
         <v>1</v>
       </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31" t="s">
+      <c r="I11" s="28"/>
+      <c r="J11" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="74"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="76"/>
+    </row>
+    <row r="12" spans="1:13" ht="18" customHeight="1">
+      <c r="A12" s="24">
+        <v>4</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="76"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.600000000000001">
+      <c r="A13" s="30">
+        <v>5</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="59"/>
+    </row>
+    <row r="14" spans="1:13" ht="18" customHeight="1">
+      <c r="A14" s="24">
+        <v>6</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="64"/>
+    </row>
+    <row r="15" spans="1:13" ht="18" customHeight="1">
+      <c r="A15" s="24">
+        <v>7</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="76"/>
+    </row>
+    <row r="16" spans="1:13" ht="18" customHeight="1">
+      <c r="A16" s="23">
+        <v>8</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="59"/>
+    </row>
+    <row r="17" spans="1:13" ht="18" customHeight="1">
+      <c r="A17" s="24">
+        <v>9</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="59"/>
+    </row>
+    <row r="18" spans="1:13" ht="18" customHeight="1">
+      <c r="A18" s="24">
+        <v>10</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="59"/>
+    </row>
+    <row r="19" spans="1:13" ht="18" customHeight="1">
+      <c r="A19" s="30">
+        <v>11</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27">
+        <v>1</v>
+      </c>
+      <c r="I19" s="28"/>
+      <c r="J19" s="29">
+        <v>688</v>
+      </c>
+      <c r="K19" s="57"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="59"/>
+    </row>
+    <row r="20" spans="1:13" ht="18" customHeight="1">
+      <c r="A20" s="24">
+        <v>12</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="27">
+        <v>1</v>
+      </c>
+      <c r="I20" s="28"/>
+      <c r="J20" s="29">
+        <v>688</v>
+      </c>
+      <c r="K20" s="62"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="64"/>
+    </row>
+    <row r="21" spans="1:13" ht="18" customHeight="1">
+      <c r="A21" s="30">
+        <v>13</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="27">
+        <v>1</v>
+      </c>
+      <c r="I21" s="28"/>
+      <c r="J21" s="29">
+        <v>688</v>
+      </c>
+      <c r="K21" s="74"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="76"/>
+    </row>
+    <row r="22" spans="1:13" ht="18" customHeight="1">
+      <c r="A22" s="24">
+        <v>14</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="27">
+        <v>1</v>
+      </c>
+      <c r="I22" s="28"/>
+      <c r="J22" s="29">
+        <v>688</v>
+      </c>
+      <c r="K22" s="57"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="59"/>
+    </row>
+    <row r="23" spans="1:13" ht="18" customHeight="1">
+      <c r="A23" s="30">
+        <v>15</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="27">
+        <v>1</v>
+      </c>
+      <c r="I23" s="28"/>
+      <c r="J23" s="29">
+        <v>688</v>
+      </c>
+      <c r="K23" s="57"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="59"/>
+    </row>
+    <row r="24" spans="1:13" ht="18" customHeight="1">
+      <c r="A24" s="24">
+        <v>16</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="59"/>
+    </row>
+    <row r="25" spans="1:13" ht="18" customHeight="1">
+      <c r="A25" s="30">
+        <v>17</v>
+      </c>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="59"/>
+    </row>
+    <row r="26" spans="1:13" ht="18" customHeight="1">
+      <c r="A26" s="24">
+        <v>18</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="73"/>
+    </row>
+    <row r="27" spans="1:13" ht="18" customHeight="1">
+      <c r="A27" s="30">
+        <v>19</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="59"/>
+    </row>
+    <row r="28" spans="1:13" ht="18" customHeight="1">
+      <c r="A28" s="24">
+        <v>20</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="58"/>
+      <c r="M28" s="59"/>
+    </row>
+    <row r="29" spans="1:13" ht="18" customHeight="1">
+      <c r="A29" s="30">
+        <v>21</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" s="58"/>
+      <c r="M29" s="59"/>
+    </row>
+    <row r="30" spans="1:13" ht="18" customHeight="1">
+      <c r="A30" s="24">
+        <v>22</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="72"/>
+      <c r="M30" s="73"/>
+    </row>
+    <row r="31" spans="1:13" ht="18" customHeight="1">
+      <c r="A31" s="30">
+        <v>23</v>
+      </c>
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="59"/>
+    </row>
+    <row r="32" spans="1:13" ht="18" customHeight="1">
+      <c r="A32" s="24">
+        <v>24</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="59"/>
+    </row>
+    <row r="33" spans="1:13" ht="18" customHeight="1">
+      <c r="A33" s="30">
+        <v>25</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="59"/>
+    </row>
+    <row r="34" spans="1:13" ht="18" customHeight="1">
+      <c r="A34" s="24">
+        <v>26</v>
+      </c>
+      <c r="B34" s="24"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="59"/>
+    </row>
+    <row r="35" spans="1:13" ht="18" customHeight="1">
+      <c r="A35" s="30">
+        <v>27</v>
+      </c>
+      <c r="B35" s="24"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="59"/>
+    </row>
+    <row r="36" spans="1:13" ht="18" customHeight="1">
+      <c r="A36" s="24">
+        <v>28</v>
+      </c>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="64"/>
+    </row>
+    <row r="37" spans="1:13" ht="18" customHeight="1">
+      <c r="A37" s="30">
+        <v>29</v>
+      </c>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+    </row>
+    <row r="38" spans="1:13" ht="18" customHeight="1">
+      <c r="A38" s="24">
+        <v>30</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="59"/>
+    </row>
+    <row r="39" spans="1:13" ht="18" customHeight="1">
+      <c r="A39" s="30"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="59"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.6" customHeight="1">
+      <c r="A40" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="60"/>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" s="24"/>
+      <c r="J40" s="34">
+        <f>(H40*$L$5)+(I40*$L$3)</f>
+        <v>4128</v>
+      </c>
+      <c r="K40" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.6" customHeight="1">
+      <c r="A41" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="34">
+        <f>H41*L5</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="68"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="70"/>
-    </row>
-    <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="26">
-        <v>4</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="70"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.600000000000001">
-      <c r="A12" s="32">
-        <v>5</v>
-      </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="53"/>
-    </row>
-    <row r="13" spans="1:13" ht="18" customHeight="1">
-      <c r="A13" s="26">
-        <v>6</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="58"/>
-    </row>
-    <row r="14" spans="1:13" ht="18" customHeight="1">
-      <c r="A14" s="26">
-        <v>7</v>
-      </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="70"/>
-    </row>
-    <row r="15" spans="1:13" ht="18" customHeight="1">
-      <c r="A15" s="25">
-        <v>8</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="53"/>
-    </row>
-    <row r="16" spans="1:13" ht="18" customHeight="1">
-      <c r="A16" s="26">
-        <v>9</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="53"/>
-    </row>
-    <row r="17" spans="1:13" ht="18" customHeight="1">
-      <c r="A17" s="26">
-        <v>10</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="53"/>
-    </row>
-    <row r="18" spans="1:13" ht="18" customHeight="1">
-      <c r="A18" s="32">
-        <v>11</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29">
-        <v>1</v>
-      </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31">
-        <v>688</v>
-      </c>
-      <c r="K18" s="51"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="53"/>
-    </row>
-    <row r="19" spans="1:13" ht="18" customHeight="1">
-      <c r="A19" s="26">
-        <v>12</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29">
-        <v>1</v>
-      </c>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31">
-        <v>688</v>
-      </c>
-      <c r="K19" s="56"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="58"/>
-    </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="32">
-        <v>13</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29">
-        <v>1</v>
-      </c>
-      <c r="I20" s="30"/>
-      <c r="J20" s="31">
-        <v>688</v>
-      </c>
-      <c r="K20" s="68"/>
-      <c r="L20" s="69"/>
-      <c r="M20" s="70"/>
-    </row>
-    <row r="21" spans="1:13" ht="18" customHeight="1">
-      <c r="A21" s="26">
-        <v>14</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29">
-        <v>1</v>
-      </c>
-      <c r="I21" s="30"/>
-      <c r="J21" s="31">
-        <v>688</v>
-      </c>
-      <c r="K21" s="51"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="53"/>
-    </row>
-    <row r="22" spans="1:13" ht="18" customHeight="1">
-      <c r="A22" s="32">
-        <v>15</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29">
-        <v>1</v>
-      </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="31">
-        <v>688</v>
-      </c>
-      <c r="K22" s="51"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="53"/>
-    </row>
-    <row r="23" spans="1:13" ht="18" customHeight="1">
-      <c r="A23" s="26">
-        <v>16</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="53"/>
-    </row>
-    <row r="24" spans="1:13" ht="18" customHeight="1">
-      <c r="A24" s="32">
-        <v>17</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="53"/>
-    </row>
-    <row r="25" spans="1:13" ht="18" customHeight="1">
-      <c r="A25" s="26">
-        <v>18</v>
-      </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="67"/>
-    </row>
-    <row r="26" spans="1:13" ht="18" customHeight="1">
-      <c r="A26" s="32">
-        <v>19</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="53"/>
-    </row>
-    <row r="27" spans="1:13" ht="18" customHeight="1">
-      <c r="A27" s="26">
-        <v>20</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="52"/>
-      <c r="M27" s="53"/>
-    </row>
-    <row r="28" spans="1:13" ht="18" customHeight="1">
-      <c r="A28" s="32">
-        <v>21</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="L28" s="52"/>
-      <c r="M28" s="53"/>
-    </row>
-    <row r="29" spans="1:13" ht="18" customHeight="1">
-      <c r="A29" s="26">
-        <v>22</v>
-      </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="L29" s="66"/>
-      <c r="M29" s="67"/>
-    </row>
-    <row r="30" spans="1:13" ht="18" customHeight="1">
-      <c r="A30" s="32">
-        <v>23</v>
-      </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="53"/>
-    </row>
-    <row r="31" spans="1:13" ht="18" customHeight="1">
-      <c r="A31" s="26">
-        <v>24</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="53"/>
-    </row>
-    <row r="32" spans="1:13" ht="18" customHeight="1">
-      <c r="A32" s="32">
-        <v>25</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="53"/>
-    </row>
-    <row r="33" spans="1:13" ht="18" customHeight="1">
-      <c r="A33" s="26">
-        <v>26</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="53"/>
-    </row>
-    <row r="34" spans="1:13" ht="18" customHeight="1">
-      <c r="A34" s="32">
-        <v>27</v>
-      </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="51"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="53"/>
-    </row>
-    <row r="35" spans="1:13" ht="18" customHeight="1">
-      <c r="A35" s="26">
-        <v>28</v>
-      </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="58"/>
-    </row>
-    <row r="36" spans="1:13" ht="18" customHeight="1">
-      <c r="A36" s="32">
-        <v>29</v>
-      </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="58"/>
-    </row>
-    <row r="37" spans="1:13" ht="18" customHeight="1">
-      <c r="A37" s="26">
-        <v>30</v>
-      </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="53"/>
-    </row>
-    <row r="38" spans="1:13" ht="18" customHeight="1">
-      <c r="A38" s="32"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="53"/>
-    </row>
-    <row r="39" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A39" s="54" t="s">
+      <c r="L41" s="66"/>
+      <c r="M41" s="67"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A42" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="36">
-        <f>(H39*$L$5)+(I39*$L$3)</f>
-        <v>4128</v>
-      </c>
-      <c r="K39" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="L39" s="57"/>
-      <c r="M39" s="58"/>
-    </row>
-    <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="54"/>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="36">
-        <f>H40*L5</f>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="34">
+        <f>I42*L3</f>
         <v>0</v>
       </c>
-      <c r="K40" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="L40" s="60"/>
-      <c r="M40" s="61"/>
-    </row>
-    <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A41" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="36">
-        <f>I41*L3</f>
-        <v>0</v>
-      </c>
-      <c r="K41" s="56" t="s">
+      <c r="K42" s="62" t="s">
         <v>38</v>
-      </c>
-      <c r="L41" s="57"/>
-      <c r="M41" s="58"/>
-    </row>
-    <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="51" t="str">
-        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
-        <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
-      </c>
-      <c r="B42" s="52"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I42" s="34"/>
-      <c r="J42" s="37">
-        <f>SUM(J39:J41)</f>
-        <v>4128</v>
-      </c>
-      <c r="K42" s="62" t="s">
-        <v>39</v>
       </c>
       <c r="L42" s="63"/>
       <c r="M42" s="64"/>
     </row>
-    <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A43" s="48" t="s">
+    <row r="43" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A43" s="57" t="str">
+        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J43)&amp;")"</f>
+        <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
+      </c>
+      <c r="B43" s="58"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="32"/>
+      <c r="J43" s="35">
+        <f>SUM(J40:J42)</f>
+        <v>4128</v>
+      </c>
+      <c r="K43" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="L43" s="69"/>
+      <c r="M43" s="70"/>
+    </row>
+    <row r="44" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
+      <c r="A44" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="48" t="s">
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="48" t="s">
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="47"/>
+      <c r="K44" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="L43" s="49"/>
-      <c r="M43" s="50"/>
-    </row>
-    <row r="44" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A44" s="39"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="41"/>
-    </row>
-    <row r="45" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A45" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="40"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="39" t="s">
+      <c r="L44" s="55"/>
+      <c r="M44" s="56"/>
+    </row>
+    <row r="45" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A45" s="45"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="47"/>
+    </row>
+    <row r="46" spans="1:13" ht="17.25" customHeight="1">
+      <c r="A46" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="39" t="s">
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="47"/>
+      <c r="K46" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="46"/>
+      <c r="M46" s="47"/>
+    </row>
+    <row r="47" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A47" s="45" t="s">
         <v>44</v>
-      </c>
-      <c r="L45" s="40"/>
-      <c r="M45" s="41"/>
-    </row>
-    <row r="46" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A46" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="L46" s="43"/>
-      <c r="M46" s="44"/>
-    </row>
-    <row r="47" spans="1:13" ht="21" customHeight="1">
-      <c r="A47" s="45" t="s">
-        <v>59</v>
       </c>
       <c r="B47" s="46"/>
       <c r="C47" s="46"/>
       <c r="D47" s="47"/>
       <c r="E47" s="45" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F47" s="46"/>
       <c r="G47" s="46"/>
       <c r="H47" s="46"/>
       <c r="I47" s="46"/>
       <c r="J47" s="47"/>
-      <c r="K47" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="L47" s="46"/>
-      <c r="M47" s="47"/>
-    </row>
-    <row r="48" spans="1:13" ht="18">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
+      <c r="K47" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="L47" s="49"/>
+      <c r="M47" s="50"/>
+    </row>
+    <row r="48" spans="1:13" ht="21" customHeight="1">
+      <c r="A48" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="L48" s="52"/>
+      <c r="M48" s="53"/>
     </row>
     <row r="49" spans="1:13" ht="18">
       <c r="A49" s="4"/>
@@ -3041,6 +3109,21 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
+    <row r="53" spans="1:13" ht="18">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="71">
     <mergeCell ref="J1:M1"/>
@@ -3049,22 +3132,21 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="K14:M14"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="K7:M7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="K17:M17"/>
@@ -3075,8 +3157,8 @@
     <mergeCell ref="K22:M22"/>
     <mergeCell ref="K23:M23"/>
     <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K38:M38"/>
     <mergeCell ref="K27:M27"/>
     <mergeCell ref="K28:M28"/>
     <mergeCell ref="K29:M29"/>
@@ -3087,12 +3169,10 @@
     <mergeCell ref="K34:M34"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:J43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="E40:G40"/>
@@ -3100,11 +3180,11 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="K41:M41"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:G42"/>
     <mergeCell ref="K42:M42"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="K43:M43"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E45:J45"/>
     <mergeCell ref="K45:M45"/>
@@ -3114,6 +3194,9 @@
     <mergeCell ref="A47:D47"/>
     <mergeCell ref="E47:J47"/>
     <mergeCell ref="K47:M47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:J48"/>
+    <mergeCell ref="K48:M48"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5770A49-0F33-470D-BD51-FA795394EC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E385FCC9-2D71-4863-9F1C-F506D01E3011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -637,7 +637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -672,21 +672,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -747,21 +732,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -771,55 +744,40 @@
     <xf numFmtId="43" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -831,43 +789,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -906,38 +828,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2062,46 +2035,46 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="77" t="s">
+      <c r="J1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="92" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="93"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="94"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="44"/>
       <c r="L3" s="10">
         <v>86</v>
       </c>
@@ -2110,944 +2083,944 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="95" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="96"/>
-    </row>
-    <row r="5" spans="1:13" ht="20.399999999999999">
-      <c r="A5" s="39" t="s">
+      <c r="M4" s="47"/>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1">
+      <c r="A5" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="42" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="98" t="s">
+      <c r="E5" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="99" t="s">
+      <c r="G5" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="77"/>
-      <c r="J5" s="100" t="s">
+      <c r="I5" s="39"/>
+      <c r="J5" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="35">
         <v>688</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="M5" s="31" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20.399999999999999">
-      <c r="A6" s="39"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13" t="s">
+      <c r="A6" s="32"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="41"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="31"/>
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="82" t="s">
+      <c r="K7" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="83"/>
-      <c r="M7" s="84"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="58"/>
     </row>
     <row r="8" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A8" s="79"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="85" t="s">
+      <c r="C8" s="55"/>
+      <c r="D8" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="85" t="s">
+      <c r="E8" s="60"/>
+      <c r="F8" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="86"/>
-      <c r="H8" s="19" t="s">
+      <c r="G8" s="60"/>
+      <c r="H8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="J8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="87" t="s">
+      <c r="K8" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="88"/>
-      <c r="M8" s="89"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="63"/>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1">
-      <c r="A9" s="23">
+      <c r="A9" s="18">
         <v>1</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="70"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="66"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="24">
+      <c r="A10" s="19">
         <v>2</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="76"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="69"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="30">
+      <c r="A11" s="25">
         <v>3</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="22">
         <v>1</v>
       </c>
-      <c r="I11" s="28"/>
-      <c r="J11" s="29" t="s">
+      <c r="I11" s="23"/>
+      <c r="J11" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="74"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="76"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="69"/>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1">
-      <c r="A12" s="24">
+      <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="76"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="69"/>
     </row>
     <row r="13" spans="1:13" ht="18.600000000000001">
-      <c r="A13" s="30">
+      <c r="A13" s="25">
         <v>5</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="59"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="72"/>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
-      <c r="A14" s="24">
+      <c r="A14" s="19">
         <v>6</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="63"/>
-      <c r="M14" s="64"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="50"/>
     </row>
     <row r="15" spans="1:13" ht="18" customHeight="1">
-      <c r="A15" s="24">
+      <c r="A15" s="19">
         <v>7</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="76"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="69"/>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1">
-      <c r="A16" s="23">
+      <c r="A16" s="18">
         <v>8</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="59"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="72"/>
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1">
-      <c r="A17" s="24">
+      <c r="A17" s="19">
         <v>9</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="59"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="72"/>
     </row>
     <row r="18" spans="1:13" ht="18" customHeight="1">
-      <c r="A18" s="24">
+      <c r="A18" s="19">
         <v>10</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="59"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="72"/>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1">
-      <c r="A19" s="30">
+      <c r="A19" s="25">
         <v>11</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="27">
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22">
         <v>1</v>
       </c>
-      <c r="I19" s="28"/>
-      <c r="J19" s="29">
+      <c r="I19" s="23"/>
+      <c r="J19" s="24">
         <v>688</v>
       </c>
-      <c r="K19" s="57"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="59"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="72"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="24">
+      <c r="A20" s="19">
         <v>12</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="27">
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22">
         <v>1</v>
       </c>
-      <c r="I20" s="28"/>
-      <c r="J20" s="29">
+      <c r="I20" s="23"/>
+      <c r="J20" s="24">
         <v>688</v>
       </c>
-      <c r="K20" s="62"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="64"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="50"/>
     </row>
     <row r="21" spans="1:13" ht="18" customHeight="1">
-      <c r="A21" s="30">
+      <c r="A21" s="25">
         <v>13</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27">
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22">
         <v>1</v>
       </c>
-      <c r="I21" s="28"/>
-      <c r="J21" s="29">
+      <c r="I21" s="23"/>
+      <c r="J21" s="24">
         <v>688</v>
       </c>
-      <c r="K21" s="74"/>
-      <c r="L21" s="75"/>
-      <c r="M21" s="76"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="69"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1">
-      <c r="A22" s="24">
+      <c r="A22" s="19">
         <v>14</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27">
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22">
         <v>1</v>
       </c>
-      <c r="I22" s="28"/>
-      <c r="J22" s="29">
+      <c r="I22" s="23"/>
+      <c r="J22" s="24">
         <v>688</v>
       </c>
-      <c r="K22" s="57"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="59"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="72"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1">
-      <c r="A23" s="30">
+      <c r="A23" s="25">
         <v>15</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="27">
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22">
         <v>1</v>
       </c>
-      <c r="I23" s="28"/>
-      <c r="J23" s="29">
+      <c r="I23" s="23"/>
+      <c r="J23" s="24">
         <v>688</v>
       </c>
-      <c r="K23" s="57"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="59"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="72"/>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1">
-      <c r="A24" s="24">
+      <c r="A24" s="19">
         <v>16</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="59"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="72"/>
     </row>
     <row r="25" spans="1:13" ht="18" customHeight="1">
-      <c r="A25" s="30">
+      <c r="A25" s="25">
         <v>17</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="59"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="72"/>
     </row>
     <row r="26" spans="1:13" ht="18" customHeight="1">
-      <c r="A26" s="24">
+      <c r="A26" s="19">
         <v>18</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="73"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="75"/>
     </row>
     <row r="27" spans="1:13" ht="18" customHeight="1">
-      <c r="A27" s="30">
+      <c r="A27" s="25">
         <v>19</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="59"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="72"/>
     </row>
     <row r="28" spans="1:13" ht="18" customHeight="1">
-      <c r="A28" s="24">
+      <c r="A28" s="19">
         <v>20</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="57" t="s">
+      <c r="B28" s="19"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="L28" s="58"/>
-      <c r="M28" s="59"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="72"/>
     </row>
     <row r="29" spans="1:13" ht="18" customHeight="1">
-      <c r="A29" s="30">
+      <c r="A29" s="25">
         <v>21</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="57" t="s">
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="L29" s="58"/>
-      <c r="M29" s="59"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="72"/>
     </row>
     <row r="30" spans="1:13" ht="18" customHeight="1">
-      <c r="A30" s="24">
+      <c r="A30" s="19">
         <v>22</v>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="71" t="s">
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="L30" s="72"/>
-      <c r="M30" s="73"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="75"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1">
-      <c r="A31" s="30">
+      <c r="A31" s="25">
         <v>23</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="59"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="72"/>
     </row>
     <row r="32" spans="1:13" ht="18" customHeight="1">
-      <c r="A32" s="24">
+      <c r="A32" s="19">
         <v>24</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="59"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="72"/>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1">
-      <c r="A33" s="30">
+      <c r="A33" s="25">
         <v>25</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="59"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="72"/>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1">
-      <c r="A34" s="24">
+      <c r="A34" s="19">
         <v>26</v>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="58"/>
-      <c r="M34" s="59"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="72"/>
     </row>
     <row r="35" spans="1:13" ht="18" customHeight="1">
-      <c r="A35" s="30">
+      <c r="A35" s="25">
         <v>27</v>
       </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="57"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="59"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="72"/>
     </row>
     <row r="36" spans="1:13" ht="18" customHeight="1">
-      <c r="A36" s="24">
+      <c r="A36" s="19">
         <v>28</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="62"/>
-      <c r="L36" s="63"/>
-      <c r="M36" s="64"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="50"/>
     </row>
     <row r="37" spans="1:13" ht="18" customHeight="1">
-      <c r="A37" s="30">
+      <c r="A37" s="25">
         <v>29</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="50"/>
     </row>
     <row r="38" spans="1:13" ht="18" customHeight="1">
-      <c r="A38" s="24">
+      <c r="A38" s="19">
         <v>30</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="59"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="72"/>
     </row>
     <row r="39" spans="1:13" ht="18" customHeight="1">
-      <c r="A39" s="30"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="58"/>
-      <c r="M39" s="59"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="72"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="60"/>
-      <c r="C40" s="60"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="61" t="s">
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="26" t="s">
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I40" s="24"/>
-      <c r="J40" s="34">
-        <f>(H40*$L$5)+(I40*$L$3)</f>
-        <v>4128</v>
-      </c>
-      <c r="K40" s="62" t="s">
+      <c r="I40" s="19"/>
+      <c r="J40" s="29">
+        <f>(H40*$L$6)+(I40*$L$3)</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="50"/>
     </row>
     <row r="41" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A41" s="60" t="s">
+      <c r="A41" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="60"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="34">
-        <f>H41*L5</f>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="29">
+        <f>H41*L6</f>
         <v>0</v>
       </c>
-      <c r="K41" s="65" t="s">
+      <c r="K41" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="66"/>
-      <c r="M41" s="67"/>
+      <c r="L41" s="83"/>
+      <c r="M41" s="84"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="60" t="s">
+      <c r="A42" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="34">
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="29">
         <f>I42*L3</f>
         <v>0</v>
       </c>
-      <c r="K42" s="62" t="s">
+      <c r="K42" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="L42" s="63"/>
-      <c r="M42" s="64"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="50"/>
     </row>
     <row r="43" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A43" s="57" t="str">
+      <c r="A43" s="70" t="str">
         <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J43)&amp;")"</f>
-        <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
-      </c>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="26" t="s">
+        <v>รวมเงิน (ศูนย์บาทถ้วน)</v>
+      </c>
+      <c r="B43" s="71"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="I43" s="32"/>
-      <c r="J43" s="35">
+      <c r="I43" s="27"/>
+      <c r="J43" s="30">
         <f>SUM(J40:J42)</f>
-        <v>4128</v>
-      </c>
-      <c r="K43" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="K43" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="L43" s="69"/>
-      <c r="M43" s="70"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="66"/>
     </row>
     <row r="44" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="54" t="s">
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="47"/>
-      <c r="K44" s="54" t="s">
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="79"/>
+      <c r="K44" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="L44" s="55"/>
-      <c r="M44" s="56"/>
+      <c r="L44" s="77"/>
+      <c r="M44" s="78"/>
     </row>
     <row r="45" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A45" s="45"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="47"/>
+      <c r="A45" s="85"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="85"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="79"/>
+      <c r="K45" s="85"/>
+      <c r="L45" s="45"/>
+      <c r="M45" s="79"/>
     </row>
     <row r="46" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="45" t="s">
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="45" t="s">
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="L46" s="46"/>
-      <c r="M46" s="47"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="79"/>
     </row>
     <row r="47" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A47" s="45" t="s">
+      <c r="A47" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="45" t="s">
+      <c r="B47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="48" t="s">
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="L47" s="49"/>
-      <c r="M47" s="50"/>
+      <c r="L47" s="87"/>
+      <c r="M47" s="88"/>
     </row>
     <row r="48" spans="1:13" ht="21" customHeight="1">
-      <c r="A48" s="51" t="s">
+      <c r="A48" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="51" t="s">
+      <c r="B48" s="90"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="91"/>
+      <c r="E48" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="F48" s="52"/>
-      <c r="G48" s="52"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="51" t="s">
+      <c r="F48" s="90"/>
+      <c r="G48" s="90"/>
+      <c r="H48" s="90"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
+      <c r="K48" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="L48" s="52"/>
-      <c r="M48" s="53"/>
+      <c r="L48" s="90"/>
+      <c r="M48" s="91"/>
     </row>
     <row r="49" spans="1:13" ht="18">
       <c r="A49" s="4"/>
@@ -3125,51 +3098,21 @@
       <c r="M53" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="K14:M14"/>
+  <mergeCells count="73">
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="E44:J44"/>
     <mergeCell ref="K44:M44"/>
@@ -3185,18 +3128,50 @@
     <mergeCell ref="K42:M42"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="K43:M43"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:J48"/>
-    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="L4:M4"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E385FCC9-2D71-4863-9F1C-F506D01E3011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD03653-99B3-44F3-8543-170F4E7FD9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>เลขที่คำขอระบบ HRIS................</t>
   </si>
@@ -193,37 +193,6 @@
   </si>
   <si>
     <t>[3]</t>
-  </si>
-  <si>
-    <t>[14]</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ปฏิบัติตามคำสั่งฯ เลขที่ รฟ.ดร. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="TH Sarabun New"/>
-        <family val="2"/>
-      </rPr>
-      <t>[7] ลว. [8]</t>
-    </r>
-  </si>
-  <si>
-    <t>[SHIFT_1]</t>
-  </si>
-  <si>
-    <t>[MONEY]</t>
-  </si>
-  <si>
-    <t>วันที่ [14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
-  </si>
-  <si>
-    <t>[1_2]</t>
   </si>
   <si>
     <r>
@@ -241,24 +210,7 @@
         <rFont val="TH Sarabun New"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">         </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="TH Sarabun New"/>
-        <family val="2"/>
-      </rPr>
-      <t>[13]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="TH Sarabun New"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">              </t>
+      <t xml:space="preserve">         [13]              </t>
     </r>
     <r>
       <rPr>
@@ -296,6 +248,34 @@
     </r>
   </si>
   <si>
+    <t>[14]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ปฏิบัติตามคำสั่งฯ เลขที่ รฟ.ดร. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="TH Sarabun New"/>
+        <family val="2"/>
+      </rPr>
+      <t>[7] ลว. [8]</t>
+    </r>
+  </si>
+  <si>
+    <t>[SHIFT_1]</t>
+  </si>
+  <si>
+    <t>[MONEY]</t>
+  </si>
+  <si>
+    <t>วันที่ [14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
+  </si>
+  <si>
     <t>(นายปฐม  ชุมวงค์)</t>
   </si>
 </sst>
@@ -309,7 +289,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -412,25 +392,6 @@
       <name val="TH Sarabun New"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <name val="TH Sarabun New"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <name val="TH Sarabun New"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u val="singleAccounting"/>
-      <sz val="12"/>
-      <name val="TH Sarabun New"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -672,6 +633,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -733,27 +712,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -789,7 +747,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -906,11 +867,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1253,7 +1214,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -2035,46 +1996,46 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="42" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="43"/>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="44"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="43"/>
       <c r="L3" s="10">
         <v>86</v>
       </c>
@@ -2083,440 +2044,452 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="46" t="s">
+      <c r="A4" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="47"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1">
-      <c r="A5" s="32" t="s">
+      <c r="M4" s="46"/>
+    </row>
+    <row r="5" spans="1:13" ht="20.399999999999999">
+      <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="50"/>
+      <c r="D5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="H5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="38" t="s">
+      <c r="I5" s="51"/>
+      <c r="J5" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="17">
         <v>688</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="M5" s="37" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="20.399999999999999">
-      <c r="A6" s="32"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="31"/>
-    </row>
-    <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="52" t="s">
+    <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
+      <c r="A6" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C6" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D6" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E6" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F6" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G6" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="56" t="s">
+      <c r="K6" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="57"/>
-      <c r="M7" s="58"/>
-    </row>
-    <row r="8" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="16" t="s">
+      <c r="L6" s="57"/>
+      <c r="M6" s="58"/>
+    </row>
+    <row r="7" spans="1:13" ht="25.5" customHeight="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="59" t="s">
+      <c r="C7" s="55"/>
+      <c r="D7" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="59" t="s">
+      <c r="E7" s="60"/>
+      <c r="F7" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="60"/>
-      <c r="H8" s="14" t="s">
+      <c r="G7" s="60"/>
+      <c r="H7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" s="62"/>
-      <c r="M8" s="63"/>
+      <c r="K7" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="62"/>
+      <c r="M7" s="63"/>
+    </row>
+    <row r="8" spans="1:13" ht="18" customHeight="1">
+      <c r="A8" s="24">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="66"/>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1">
-      <c r="A9" s="18">
+      <c r="A9" s="25">
+        <v>2</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="69"/>
+    </row>
+    <row r="10" spans="1:13" ht="18" customHeight="1">
+      <c r="A10" s="31">
+        <v>3</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="28">
         <v>1</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="66"/>
-    </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="19">
-        <v>2</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30" t="s">
+        <v>57</v>
+      </c>
       <c r="K10" s="67"/>
       <c r="L10" s="68"/>
       <c r="M10" s="69"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
       <c r="A11" s="25">
-        <v>3</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="22">
-        <v>1</v>
-      </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="24" t="s">
-        <v>56</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
       <c r="K11" s="67"/>
       <c r="L11" s="68"/>
       <c r="M11" s="69"/>
     </row>
-    <row r="12" spans="1:13" ht="18" customHeight="1">
-      <c r="A12" s="19">
-        <v>4</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="69"/>
-    </row>
-    <row r="13" spans="1:13" ht="18.600000000000001">
+    <row r="12" spans="1:13" ht="18.600000000000001">
+      <c r="A12" s="31">
+        <v>5</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="72"/>
+    </row>
+    <row r="13" spans="1:13" ht="18" customHeight="1">
       <c r="A13" s="25">
-        <v>5</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="72"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="49"/>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
-      <c r="A14" s="19">
-        <v>6</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="50"/>
+      <c r="A14" s="25">
+        <v>7</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="15" spans="1:13" ht="18" customHeight="1">
-      <c r="A15" s="19">
-        <v>7</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="69"/>
+      <c r="A15" s="24">
+        <v>8</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="72"/>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1">
-      <c r="A16" s="18">
-        <v>8</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="24"/>
+      <c r="A16" s="25">
+        <v>9</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
       <c r="K16" s="70"/>
       <c r="L16" s="71"/>
       <c r="M16" s="72"/>
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1">
-      <c r="A17" s="19">
-        <v>9</v>
-      </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="24"/>
+      <c r="A17" s="25">
+        <v>10</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="30"/>
       <c r="K17" s="70"/>
       <c r="L17" s="71"/>
       <c r="M17" s="72"/>
     </row>
     <row r="18" spans="1:13" ht="18" customHeight="1">
-      <c r="A18" s="19">
-        <v>10</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="24"/>
+      <c r="A18" s="31">
+        <v>11</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="28">
+        <v>1</v>
+      </c>
+      <c r="I18" s="29"/>
+      <c r="J18" s="30">
+        <v>688</v>
+      </c>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="72"/>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1">
       <c r="A19" s="25">
-        <v>11</v>
-      </c>
-      <c r="B19" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="22">
+      <c r="D19" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="28">
         <v>1</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24">
+      <c r="I19" s="29"/>
+      <c r="J19" s="30">
         <v>688</v>
       </c>
-      <c r="K19" s="70"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="72"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="49"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="19">
-        <v>12</v>
-      </c>
-      <c r="B20" s="19" t="s">
+      <c r="A20" s="31">
+        <v>13</v>
+      </c>
+      <c r="B20" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="22">
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="28">
         <v>1</v>
       </c>
-      <c r="I20" s="23"/>
-      <c r="J20" s="24">
+      <c r="I20" s="29"/>
+      <c r="J20" s="30">
         <v>688</v>
       </c>
-      <c r="K20" s="48"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="50"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="69"/>
     </row>
     <row r="21" spans="1:13" ht="18" customHeight="1">
       <c r="A21" s="25">
-        <v>13</v>
-      </c>
-      <c r="B21" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22">
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="28">
         <v>1</v>
       </c>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24">
+      <c r="I21" s="29"/>
+      <c r="J21" s="30">
         <v>688</v>
       </c>
-      <c r="K21" s="67"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="69"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="72"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1">
-      <c r="A22" s="19">
-        <v>14</v>
-      </c>
-      <c r="B22" s="19" t="s">
+      <c r="A22" s="31">
+        <v>15</v>
+      </c>
+      <c r="B22" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="22">
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="28">
         <v>1</v>
       </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="24">
+      <c r="I22" s="29"/>
+      <c r="J22" s="30">
         <v>688</v>
       </c>
       <c r="K22" s="70"/>
@@ -2525,308 +2498,305 @@
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1">
       <c r="A23" s="25">
-        <v>15</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="22">
-        <v>1</v>
-      </c>
-      <c r="I23" s="23"/>
-      <c r="J23" s="24">
-        <v>688</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="30"/>
       <c r="K23" s="70"/>
       <c r="L23" s="71"/>
       <c r="M23" s="72"/>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1">
-      <c r="A24" s="19">
-        <v>16</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="24"/>
+      <c r="A24" s="31">
+        <v>17</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="70"/>
       <c r="L24" s="71"/>
       <c r="M24" s="72"/>
     </row>
     <row r="25" spans="1:13" ht="18" customHeight="1">
       <c r="A25" s="25">
-        <v>17</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="72"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="1:13" ht="18" customHeight="1">
-      <c r="A26" s="19">
-        <v>18</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="75"/>
+      <c r="A26" s="31">
+        <v>19</v>
+      </c>
+      <c r="B26" s="25"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="72"/>
     </row>
     <row r="27" spans="1:13" ht="18" customHeight="1">
       <c r="A27" s="25">
-        <v>19</v>
-      </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="70"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="70" t="s">
+        <v>32</v>
+      </c>
       <c r="L27" s="71"/>
       <c r="M27" s="72"/>
     </row>
     <row r="28" spans="1:13" ht="18" customHeight="1">
-      <c r="A28" s="19">
-        <v>20</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="24"/>
+      <c r="A28" s="31">
+        <v>21</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="30"/>
       <c r="K28" s="70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L28" s="71"/>
       <c r="M28" s="72"/>
     </row>
     <row r="29" spans="1:13" ht="18" customHeight="1">
       <c r="A29" s="25">
-        <v>21</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="L29" s="71"/>
-      <c r="M29" s="72"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
     </row>
     <row r="30" spans="1:13" ht="18" customHeight="1">
-      <c r="A30" s="19">
-        <v>22</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="74"/>
-      <c r="M30" s="75"/>
+      <c r="A30" s="31">
+        <v>23</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="72"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1">
       <c r="A31" s="25">
-        <v>23</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="24"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="30"/>
       <c r="K31" s="70"/>
       <c r="L31" s="71"/>
       <c r="M31" s="72"/>
     </row>
     <row r="32" spans="1:13" ht="18" customHeight="1">
-      <c r="A32" s="19">
-        <v>24</v>
-      </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="24"/>
+      <c r="A32" s="31">
+        <v>25</v>
+      </c>
+      <c r="B32" s="25"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
       <c r="K32" s="70"/>
       <c r="L32" s="71"/>
       <c r="M32" s="72"/>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1">
       <c r="A33" s="25">
-        <v>25</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="24"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="30"/>
       <c r="K33" s="70"/>
       <c r="L33" s="71"/>
       <c r="M33" s="72"/>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1">
-      <c r="A34" s="19">
-        <v>26</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="24"/>
+      <c r="A34" s="31">
+        <v>27</v>
+      </c>
+      <c r="B34" s="25"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="30"/>
       <c r="K34" s="70"/>
       <c r="L34" s="71"/>
       <c r="M34" s="72"/>
     </row>
     <row r="35" spans="1:13" ht="18" customHeight="1">
       <c r="A35" s="25">
-        <v>27</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="72"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="49"/>
     </row>
     <row r="36" spans="1:13" ht="18" customHeight="1">
-      <c r="A36" s="19">
-        <v>28</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="50"/>
+      <c r="A36" s="31">
+        <v>29</v>
+      </c>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="49"/>
     </row>
     <row r="37" spans="1:13" ht="18" customHeight="1">
       <c r="A37" s="25">
-        <v>29</v>
-      </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="50"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="72"/>
     </row>
     <row r="38" spans="1:13" ht="18" customHeight="1">
-      <c r="A38" s="19">
-        <v>30</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="24"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="30"/>
       <c r="K38" s="70"/>
       <c r="L38" s="71"/>
       <c r="M38" s="72"/>
     </row>
-    <row r="39" spans="1:13" ht="18" customHeight="1">
-      <c r="A39" s="25"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="70"/>
-      <c r="L39" s="71"/>
-      <c r="M39" s="72"/>
+    <row r="39" spans="1:13" ht="15.6" customHeight="1">
+      <c r="A39" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="25"/>
+      <c r="J39" s="35">
+        <f>(H39*$L$5)+(I39*$L$3)</f>
+        <v>4128</v>
+      </c>
+      <c r="K39" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L39" s="48"/>
+      <c r="M39" s="49"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" customHeight="1">
       <c r="A40" s="80" t="s">
@@ -2835,26 +2805,22 @@
       <c r="B40" s="80"/>
       <c r="C40" s="80"/>
       <c r="D40" s="80"/>
-      <c r="E40" s="81" t="s">
-        <v>35</v>
-      </c>
+      <c r="E40" s="81"/>
       <c r="F40" s="81"/>
       <c r="G40" s="81"/>
-      <c r="H40" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="29">
-        <f>(H40*$L$6)+(I40*$L$3)</f>
+      <c r="H40" s="27"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="35">
+        <f>H40*L5</f>
         <v>0</v>
       </c>
-      <c r="K40" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="L40" s="49"/>
-      <c r="M40" s="50"/>
-    </row>
-    <row r="41" spans="1:13" ht="15.6" customHeight="1">
+      <c r="K40" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" s="83"/>
+      <c r="M40" s="84"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="80" t="s">
         <v>34</v>
       </c>
@@ -2864,163 +2830,156 @@
       <c r="E41" s="81"/>
       <c r="F41" s="81"/>
       <c r="G41" s="81"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="29">
-        <f>H41*L6</f>
+      <c r="H41" s="34"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="35">
+        <f>I41*L3</f>
         <v>0</v>
       </c>
-      <c r="K41" s="82" t="s">
-        <v>58</v>
-      </c>
-      <c r="L41" s="83"/>
-      <c r="M41" s="84"/>
+      <c r="K41" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="48"/>
+      <c r="M41" s="49"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="80" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="29">
-        <f>I42*L3</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="49"/>
-      <c r="M42" s="50"/>
-    </row>
-    <row r="43" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A43" s="70" t="str">
-        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J43)&amp;")"</f>
-        <v>รวมเงิน (ศูนย์บาทถ้วน)</v>
-      </c>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="71"/>
-      <c r="H43" s="21" t="s">
+      <c r="A42" s="70" t="str">
+        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
+        <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
+      </c>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="I43" s="27"/>
-      <c r="J43" s="30">
-        <f>SUM(J40:J42)</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="64" t="s">
+      <c r="I42" s="33"/>
+      <c r="J42" s="36">
+        <f>SUM(J39:J41)</f>
+        <v>4128</v>
+      </c>
+      <c r="K42" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="L43" s="65"/>
-      <c r="M43" s="66"/>
-    </row>
-    <row r="44" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A44" s="76" t="s">
+      <c r="L42" s="65"/>
+      <c r="M42" s="66"/>
+    </row>
+    <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
+      <c r="A43" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="76" t="s">
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="L43" s="77"/>
+      <c r="M43" s="78"/>
+    </row>
+    <row r="44" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A44" s="85"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
       <c r="J44" s="79"/>
-      <c r="K44" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="L44" s="77"/>
-      <c r="M44" s="78"/>
-    </row>
-    <row r="45" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A45" s="85"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="44"/>
+      <c r="M44" s="79"/>
+    </row>
+    <row r="45" spans="1:13" ht="17.25" customHeight="1">
+      <c r="A45" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
       <c r="D45" s="79"/>
-      <c r="E45" s="85"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
+      <c r="E45" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
       <c r="J45" s="79"/>
-      <c r="K45" s="85"/>
-      <c r="L45" s="45"/>
+      <c r="K45" s="85" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" s="44"/>
       <c r="M45" s="79"/>
     </row>
-    <row r="46" spans="1:13" ht="17.25" customHeight="1">
+    <row r="46" spans="1:13" ht="19.5" customHeight="1">
       <c r="A46" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
+        <v>44</v>
+      </c>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
       <c r="D46" s="79"/>
       <c r="E46" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
+        <v>45</v>
+      </c>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
       <c r="J46" s="79"/>
-      <c r="K46" s="85" t="s">
-        <v>61</v>
-      </c>
-      <c r="L46" s="45"/>
-      <c r="M46" s="79"/>
-    </row>
-    <row r="47" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A47" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="85" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="79"/>
-      <c r="K47" s="86" t="s">
+      <c r="K46" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="L47" s="87"/>
-      <c r="M47" s="88"/>
-    </row>
-    <row r="48" spans="1:13" ht="21" customHeight="1">
-      <c r="A48" s="89" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="90"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="91"/>
-      <c r="E48" s="89" t="s">
+      <c r="L46" s="87"/>
+      <c r="M46" s="88"/>
+    </row>
+    <row r="47" spans="1:13" ht="21" customHeight="1">
+      <c r="A47" s="89" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="50"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="F48" s="90"/>
-      <c r="G48" s="90"/>
-      <c r="H48" s="90"/>
-      <c r="I48" s="90"/>
-      <c r="J48" s="91"/>
-      <c r="K48" s="89" t="s">
+      <c r="F47" s="50"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="90"/>
+      <c r="K47" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="L48" s="90"/>
-      <c r="M48" s="91"/>
+      <c r="L47" s="50"/>
+      <c r="M47" s="90"/>
+    </row>
+    <row r="48" spans="1:13" ht="18">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13" ht="18">
       <c r="A49" s="4"/>
@@ -3082,40 +3041,26 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="1:13" ht="18">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
+  <mergeCells count="71">
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
     <mergeCell ref="A47:D47"/>
     <mergeCell ref="E47:J47"/>
     <mergeCell ref="K47:M47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:J48"/>
-    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E45:J45"/>
     <mergeCell ref="K45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:J43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:G39"/>
     <mergeCell ref="K39:M39"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="E40:G40"/>
@@ -3123,12 +3068,10 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="K41:M41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="K42:M42"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="K27:M27"/>
     <mergeCell ref="K28:M28"/>
     <mergeCell ref="K29:M29"/>
@@ -3139,8 +3082,8 @@
     <mergeCell ref="K34:M34"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K14:M14"/>
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="K17:M17"/>
@@ -3151,21 +3094,20 @@
     <mergeCell ref="K22:M22"/>
     <mergeCell ref="K23:M23"/>
     <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
     <mergeCell ref="K7:M7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K13:M13"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="L2:M2"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD03653-99B3-44F3-8543-170F4E7FD9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D3F722-207A-4695-8DFF-2E75896710C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -636,12 +636,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -711,31 +705,55 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -747,10 +765,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -789,89 +837,41 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1214,15 +1214,15 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.109375" style="2" customWidth="1"/>
     <col min="4" max="7" width="7.6640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="5.109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="4.5546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.88671875" style="1" customWidth="1"/>
@@ -1986,1000 +1986,986 @@
     <col min="16121" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="38" t="s">
+    <row r="1" spans="1:13" ht="6" customHeight="1"/>
+    <row r="2" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-    </row>
-    <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+    </row>
+    <row r="3" spans="1:13" ht="14.4" customHeight="1">
+      <c r="A3" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41" t="s">
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="42"/>
-    </row>
-    <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="M3" s="84"/>
+    </row>
+    <row r="4" spans="1:13" ht="14.4" customHeight="1">
+      <c r="A4" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="10">
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="10">
         <v>86</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M4" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="44" t="s">
+    <row r="5" spans="1:13" ht="15" customHeight="1">
+      <c r="A5" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="45" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="46"/>
-    </row>
-    <row r="5" spans="1:13" ht="20.399999999999999">
-      <c r="A5" s="12" t="s">
+      <c r="M5" s="87"/>
+    </row>
+    <row r="6" spans="1:13" ht="20.399999999999999">
+      <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B6" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="D6" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="E6" s="89"/>
+      <c r="F6" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G6" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H6" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="16" t="s">
+      <c r="I6" s="90"/>
+      <c r="J6" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L6" s="15">
         <v>688</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M6" s="35" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="52" t="s">
+    <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1">
+      <c r="A7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C7" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="56" t="s">
+      <c r="K7" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="57"/>
-      <c r="M6" s="58"/>
-    </row>
-    <row r="7" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="22" t="s">
+      <c r="L7" s="73"/>
+      <c r="M7" s="74"/>
+    </row>
+    <row r="8" spans="1:13" ht="25.5" customHeight="1">
+      <c r="A8" s="69"/>
+      <c r="B8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="59" t="s">
+      <c r="C8" s="71"/>
+      <c r="D8" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="59" t="s">
+      <c r="E8" s="76"/>
+      <c r="F8" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="60"/>
-      <c r="H7" s="20" t="s">
+      <c r="G8" s="76"/>
+      <c r="H8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="61" t="s">
+      <c r="K8" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
-    </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1">
-      <c r="A8" s="24">
+      <c r="L8" s="78"/>
+      <c r="M8" s="79"/>
+    </row>
+    <row r="9" spans="1:13" ht="18" customHeight="1">
+      <c r="A9" s="22">
         <v>1</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="65"/>
-      <c r="M8" s="66"/>
-    </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1">
-      <c r="A9" s="25">
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="61"/>
+    </row>
+    <row r="10" spans="1:13" ht="18" customHeight="1">
+      <c r="A10" s="23">
         <v>2</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="69"/>
-    </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="31">
+      <c r="B10" s="23"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="67"/>
+    </row>
+    <row r="11" spans="1:13" ht="18" customHeight="1">
+      <c r="A11" s="29">
         <v>3</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B11" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C11" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D11" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E11" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G11" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H11" s="26">
         <v>1</v>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="30" t="s">
+      <c r="I11" s="27"/>
+      <c r="J11" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="67"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="69"/>
-    </row>
-    <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="25">
+      <c r="K11" s="65"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="67"/>
+    </row>
+    <row r="12" spans="1:13" ht="18" customHeight="1">
+      <c r="A12" s="23">
         <v>4</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="69"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.600000000000001">
-      <c r="A12" s="31">
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="67"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.600000000000001">
+      <c r="A13" s="29">
         <v>5</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="70"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="72"/>
-    </row>
-    <row r="13" spans="1:13" ht="18" customHeight="1">
-      <c r="A13" s="25">
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="50"/>
+    </row>
+    <row r="14" spans="1:13" ht="18" customHeight="1">
+      <c r="A14" s="23">
         <v>6</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="49"/>
-    </row>
-    <row r="14" spans="1:13" ht="18" customHeight="1">
-      <c r="A14" s="25">
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="55"/>
+    </row>
+    <row r="15" spans="1:13" ht="18" customHeight="1">
+      <c r="A15" s="23">
         <v>7</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="69"/>
-    </row>
-    <row r="15" spans="1:13" ht="18" customHeight="1">
-      <c r="A15" s="24">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="67"/>
+    </row>
+    <row r="16" spans="1:13" ht="18" customHeight="1">
+      <c r="A16" s="22">
         <v>8</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="72"/>
-    </row>
-    <row r="16" spans="1:13" ht="18" customHeight="1">
-      <c r="A16" s="25">
+      <c r="B16" s="23"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="50"/>
+    </row>
+    <row r="17" spans="1:13" ht="18" customHeight="1">
+      <c r="A17" s="23">
         <v>9</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="72"/>
-    </row>
-    <row r="17" spans="1:13" ht="18" customHeight="1">
-      <c r="A17" s="25">
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="50"/>
+    </row>
+    <row r="18" spans="1:13" ht="18" customHeight="1">
+      <c r="A18" s="23">
         <v>10</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="72"/>
-    </row>
-    <row r="18" spans="1:13" ht="18" customHeight="1">
-      <c r="A18" s="31">
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="50"/>
+    </row>
+    <row r="19" spans="1:13" ht="18" customHeight="1">
+      <c r="A19" s="29">
         <v>11</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B19" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C19" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D19" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E19" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28">
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="26">
         <v>1</v>
       </c>
-      <c r="I18" s="29"/>
-      <c r="J18" s="30">
+      <c r="I19" s="27"/>
+      <c r="J19" s="28">
         <v>688</v>
       </c>
-      <c r="K18" s="70"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="72"/>
-    </row>
-    <row r="19" spans="1:13" ht="18" customHeight="1">
-      <c r="A19" s="25">
+      <c r="K19" s="48"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="50"/>
+    </row>
+    <row r="20" spans="1:13" ht="18" customHeight="1">
+      <c r="A20" s="23">
         <v>12</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B20" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C20" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D20" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E20" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28">
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="26">
         <v>1</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="30">
+      <c r="I20" s="27"/>
+      <c r="J20" s="28">
         <v>688</v>
       </c>
-      <c r="K19" s="47"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="49"/>
-    </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="31">
+      <c r="K20" s="53"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="55"/>
+    </row>
+    <row r="21" spans="1:13" ht="18" customHeight="1">
+      <c r="A21" s="29">
         <v>13</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C21" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D21" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E21" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28">
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26">
         <v>1</v>
       </c>
-      <c r="I20" s="29"/>
-      <c r="J20" s="30">
+      <c r="I21" s="27"/>
+      <c r="J21" s="28">
         <v>688</v>
       </c>
-      <c r="K20" s="67"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="69"/>
-    </row>
-    <row r="21" spans="1:13" ht="18" customHeight="1">
-      <c r="A21" s="25">
+      <c r="K21" s="65"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="67"/>
+    </row>
+    <row r="22" spans="1:13" ht="18" customHeight="1">
+      <c r="A22" s="23">
         <v>14</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B22" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C22" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D22" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E22" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28">
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26">
         <v>1</v>
       </c>
-      <c r="I21" s="29"/>
-      <c r="J21" s="30">
+      <c r="I22" s="27"/>
+      <c r="J22" s="28">
         <v>688</v>
       </c>
-      <c r="K21" s="70"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="72"/>
-    </row>
-    <row r="22" spans="1:13" ht="18" customHeight="1">
-      <c r="A22" s="31">
+      <c r="K22" s="48"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="50"/>
+    </row>
+    <row r="23" spans="1:13" ht="18" customHeight="1">
+      <c r="A23" s="29">
         <v>15</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B23" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C23" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D23" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E23" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="28">
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="26">
         <v>1</v>
       </c>
-      <c r="I22" s="29"/>
-      <c r="J22" s="30">
+      <c r="I23" s="27"/>
+      <c r="J23" s="28">
         <v>688</v>
       </c>
-      <c r="K22" s="70"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="72"/>
-    </row>
-    <row r="23" spans="1:13" ht="18" customHeight="1">
-      <c r="A23" s="25">
+      <c r="K23" s="48"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="50"/>
+    </row>
+    <row r="24" spans="1:13" ht="18" customHeight="1">
+      <c r="A24" s="23">
         <v>16</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="72"/>
-    </row>
-    <row r="24" spans="1:13" ht="18" customHeight="1">
-      <c r="A24" s="31">
+      <c r="B24" s="23"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="50"/>
+    </row>
+    <row r="25" spans="1:13" ht="18" customHeight="1">
+      <c r="A25" s="29">
         <v>17</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="72"/>
-    </row>
-    <row r="25" spans="1:13" ht="18" customHeight="1">
-      <c r="A25" s="25">
+      <c r="B25" s="23"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="50"/>
+    </row>
+    <row r="26" spans="1:13" ht="18" customHeight="1">
+      <c r="A26" s="23">
         <v>18</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="75"/>
-    </row>
-    <row r="26" spans="1:13" ht="18" customHeight="1">
-      <c r="A26" s="31">
+      <c r="B26" s="23"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="64"/>
+    </row>
+    <row r="27" spans="1:13" ht="18" customHeight="1">
+      <c r="A27" s="29">
         <v>19</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="72"/>
-    </row>
-    <row r="27" spans="1:13" ht="18" customHeight="1">
-      <c r="A27" s="25">
+      <c r="B27" s="23"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="50"/>
+    </row>
+    <row r="28" spans="1:13" ht="18" customHeight="1">
+      <c r="A28" s="23">
         <v>20</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="70" t="s">
+      <c r="B28" s="23"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="71"/>
-      <c r="M27" s="72"/>
-    </row>
-    <row r="28" spans="1:13" ht="18" customHeight="1">
-      <c r="A28" s="31">
+      <c r="L28" s="49"/>
+      <c r="M28" s="50"/>
+    </row>
+    <row r="29" spans="1:13" ht="18" customHeight="1">
+      <c r="A29" s="29">
         <v>21</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="70" t="s">
+      <c r="B29" s="23"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="L28" s="71"/>
-      <c r="M28" s="72"/>
-    </row>
-    <row r="29" spans="1:13" ht="18" customHeight="1">
-      <c r="A29" s="25">
+      <c r="L29" s="49"/>
+      <c r="M29" s="50"/>
+    </row>
+    <row r="30" spans="1:13" ht="18" customHeight="1">
+      <c r="A30" s="23">
         <v>22</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="73" t="s">
+      <c r="B30" s="23"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="L29" s="74"/>
-      <c r="M29" s="75"/>
-    </row>
-    <row r="30" spans="1:13" ht="18" customHeight="1">
-      <c r="A30" s="31">
+      <c r="L30" s="63"/>
+      <c r="M30" s="64"/>
+    </row>
+    <row r="31" spans="1:13" ht="18" customHeight="1">
+      <c r="A31" s="29">
         <v>23</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="72"/>
-    </row>
-    <row r="31" spans="1:13" ht="18" customHeight="1">
-      <c r="A31" s="25">
+      <c r="B31" s="23"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="49"/>
+      <c r="M31" s="50"/>
+    </row>
+    <row r="32" spans="1:13" ht="18" customHeight="1">
+      <c r="A32" s="23">
         <v>24</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="72"/>
-    </row>
-    <row r="32" spans="1:13" ht="18" customHeight="1">
-      <c r="A32" s="31">
+      <c r="B32" s="23"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="50"/>
+    </row>
+    <row r="33" spans="1:13" ht="18" customHeight="1">
+      <c r="A33" s="29">
         <v>25</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="70"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="72"/>
-    </row>
-    <row r="33" spans="1:13" ht="18" customHeight="1">
-      <c r="A33" s="25">
+      <c r="B33" s="23"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="50"/>
+    </row>
+    <row r="34" spans="1:13" ht="18" customHeight="1">
+      <c r="A34" s="23">
         <v>26</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="70"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="72"/>
-    </row>
-    <row r="34" spans="1:13" ht="18" customHeight="1">
-      <c r="A34" s="31">
+      <c r="B34" s="23"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="50"/>
+    </row>
+    <row r="35" spans="1:13" ht="18" customHeight="1">
+      <c r="A35" s="29">
         <v>27</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="72"/>
-    </row>
-    <row r="35" spans="1:13" ht="18" customHeight="1">
-      <c r="A35" s="25">
+      <c r="B35" s="23"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="50"/>
+    </row>
+    <row r="36" spans="1:13" ht="18" customHeight="1">
+      <c r="A36" s="23">
         <v>28</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="49"/>
-    </row>
-    <row r="36" spans="1:13" ht="18" customHeight="1">
-      <c r="A36" s="31">
+      <c r="B36" s="23"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="55"/>
+    </row>
+    <row r="37" spans="1:13" ht="18" customHeight="1">
+      <c r="A37" s="29">
         <v>29</v>
       </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="49"/>
-    </row>
-    <row r="37" spans="1:13" ht="18" customHeight="1">
-      <c r="A37" s="25">
+      <c r="B37" s="23"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="55"/>
+    </row>
+    <row r="38" spans="1:13" ht="18" customHeight="1">
+      <c r="A38" s="23">
         <v>30</v>
       </c>
-      <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="71"/>
-      <c r="M37" s="72"/>
-    </row>
-    <row r="38" spans="1:13" ht="18" customHeight="1">
-      <c r="A38" s="31"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="71"/>
-      <c r="M38" s="72"/>
-    </row>
-    <row r="39" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A39" s="80" t="s">
+      <c r="B38" s="23"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="50"/>
+    </row>
+    <row r="39" spans="1:13" ht="18" customHeight="1">
+      <c r="A39" s="29"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="48"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="50"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.6" customHeight="1">
+      <c r="A40" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="80"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="81" t="s">
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="27" t="s">
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I39" s="25"/>
-      <c r="J39" s="35">
-        <f>(H39*$L$5)+(I39*$L$3)</f>
+      <c r="I40" s="23"/>
+      <c r="J40" s="33">
+        <f>(H40*$L$6)+(I40*$L$4)</f>
         <v>4128</v>
       </c>
-      <c r="K39" s="47" t="s">
+      <c r="K40" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="L39" s="48"/>
-      <c r="M39" s="49"/>
-    </row>
-    <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="80" t="s">
+      <c r="L40" s="54"/>
+      <c r="M40" s="55"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.6" customHeight="1">
+      <c r="A41" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="35">
-        <f>H40*L5</f>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="33">
+        <f>H41*L6</f>
         <v>0</v>
       </c>
-      <c r="K40" s="82" t="s">
+      <c r="K41" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="L40" s="83"/>
-      <c r="M40" s="84"/>
-    </row>
-    <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A41" s="80" t="s">
+      <c r="L41" s="57"/>
+      <c r="M41" s="58"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A42" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="80"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="35">
-        <f>I41*L3</f>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="33">
+        <f>I42*L4</f>
         <v>0</v>
       </c>
-      <c r="K41" s="47" t="s">
+      <c r="K42" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="48"/>
-      <c r="M41" s="49"/>
-    </row>
-    <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="70" t="str">
-        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
+      <c r="L42" s="54"/>
+      <c r="M42" s="55"/>
+    </row>
+    <row r="43" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A43" s="48" t="str">
+        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J43)&amp;")"</f>
         <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="27" t="s">
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I42" s="33"/>
-      <c r="J42" s="36">
-        <f>SUM(J39:J41)</f>
+      <c r="I43" s="31"/>
+      <c r="J43" s="34">
+        <f>SUM(J40:J42)</f>
         <v>4128</v>
       </c>
-      <c r="K42" s="64" t="s">
+      <c r="K43" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="L42" s="65"/>
-      <c r="M42" s="66"/>
-    </row>
-    <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A43" s="76" t="s">
+      <c r="L43" s="60"/>
+      <c r="M43" s="61"/>
+    </row>
+    <row r="44" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
+      <c r="A44" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="76" t="s">
+      <c r="B44" s="46"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-      <c r="J43" s="79"/>
-      <c r="K43" s="76" t="s">
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="L43" s="77"/>
-      <c r="M43" s="78"/>
-    </row>
-    <row r="44" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A44" s="85"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="85"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="79"/>
-      <c r="K44" s="85"/>
-      <c r="L44" s="44"/>
-      <c r="M44" s="79"/>
-    </row>
-    <row r="45" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A45" s="85" t="s">
+      <c r="L44" s="46"/>
+      <c r="M44" s="47"/>
+    </row>
+    <row r="45" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="37"/>
+      <c r="M45" s="38"/>
+    </row>
+    <row r="46" spans="1:13" ht="17.25" customHeight="1">
+      <c r="A46" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="85" t="s">
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="79"/>
-      <c r="K45" s="85" t="s">
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="38"/>
+      <c r="K46" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="L45" s="44"/>
-      <c r="M45" s="79"/>
-    </row>
-    <row r="46" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A46" s="85" t="s">
+      <c r="L46" s="37"/>
+      <c r="M46" s="38"/>
+    </row>
+    <row r="47" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A47" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="85" t="s">
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="79"/>
-      <c r="K46" s="86" t="s">
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="38"/>
+      <c r="K47" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="87"/>
-      <c r="M46" s="88"/>
-    </row>
-    <row r="47" spans="1:13" ht="21" customHeight="1">
-      <c r="A47" s="89" t="s">
+      <c r="L47" s="40"/>
+      <c r="M47" s="41"/>
+    </row>
+    <row r="48" spans="1:13" ht="21" customHeight="1">
+      <c r="A48" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="50"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="90"/>
-      <c r="E47" s="89" t="s">
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="F47" s="50"/>
-      <c r="G47" s="50"/>
-      <c r="H47" s="50"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="90"/>
-      <c r="K47" s="89" t="s">
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="L47" s="50"/>
-      <c r="M47" s="90"/>
-    </row>
-    <row r="48" spans="1:13" ht="18">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="44"/>
     </row>
     <row r="49" spans="1:13" ht="18">
       <c r="A49" s="4"/>
@@ -3041,37 +3027,56 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
+    <row r="53" spans="1:13" ht="18">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:J43"/>
-    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K25:M25"/>
     <mergeCell ref="K38:M38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="K42:M42"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K26:M26"/>
     <mergeCell ref="K27:M27"/>
     <mergeCell ref="K28:M28"/>
     <mergeCell ref="K29:M29"/>
@@ -3082,38 +3087,34 @@
     <mergeCell ref="K34:M34"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:J48"/>
+    <mergeCell ref="K48:M48"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D3F722-207A-4695-8DFF-2E75896710C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719A5C53-6212-4EC4-94A1-20F514B9F29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -705,55 +705,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -765,40 +747,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -837,40 +786,91 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1214,7 +1214,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -1986,189 +1986,205 @@
     <col min="16121" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="6" customHeight="1"/>
-    <row r="2" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="80" t="s">
+    <row r="1" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.4" customHeight="1">
+      <c r="A2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="10">
+        <v>86</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1">
+      <c r="A4" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" s="46"/>
+    </row>
+    <row r="5" spans="1:13" ht="20.399999999999999">
+      <c r="A5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="72"/>
+      <c r="F5" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="50"/>
+      <c r="J5" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15">
+        <v>688</v>
+      </c>
+      <c r="M5" s="35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="56"/>
+      <c r="M6" s="57"/>
+    </row>
+    <row r="7" spans="1:13" ht="25.5" customHeight="1">
+      <c r="A7" s="52"/>
+      <c r="B7" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="54"/>
+      <c r="D7" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="59"/>
+      <c r="F7" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="59"/>
+      <c r="H7" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="61"/>
+      <c r="M7" s="62"/>
+    </row>
+    <row r="8" spans="1:13" ht="18" customHeight="1">
+      <c r="A8" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="83" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="65"/>
+    </row>
+    <row r="9" spans="1:13" ht="18" customHeight="1">
+      <c r="A9" s="23">
         <v>2</v>
-      </c>
-      <c r="M3" s="84"/>
-    </row>
-    <row r="4" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A4" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="10">
-        <v>86</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1">
-      <c r="A5" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="86" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5" s="87"/>
-    </row>
-    <row r="6" spans="1:13" ht="20.399999999999999">
-      <c r="A6" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="88" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="89" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="89"/>
-      <c r="F6" s="91" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="90" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="90"/>
-      <c r="J6" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="15">
-        <v>688</v>
-      </c>
-      <c r="M6" s="35" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="73"/>
-      <c r="M7" s="74"/>
-    </row>
-    <row r="8" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A8" s="69"/>
-      <c r="B8" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="75" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="76"/>
-      <c r="F8" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="78"/>
-      <c r="M8" s="79"/>
-    </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1">
-      <c r="A9" s="22">
-        <v>1</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="24"/>
@@ -2179,63 +2195,63 @@
       <c r="H9" s="26"/>
       <c r="I9" s="27"/>
       <c r="J9" s="28"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="61"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="68"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="23">
-        <v>2</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26"/>
+      <c r="A10" s="29">
+        <v>3</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="26">
+        <v>1</v>
+      </c>
       <c r="I10" s="27"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="66"/>
-      <c r="M10" s="67"/>
+      <c r="J10" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="66"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="68"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="29">
-        <v>3</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="26">
-        <v>1</v>
-      </c>
+      <c r="A11" s="23">
+        <v>4</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26"/>
       <c r="I11" s="27"/>
-      <c r="J11" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" s="65"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="67"/>
-    </row>
-    <row r="12" spans="1:13" ht="18" customHeight="1">
-      <c r="A12" s="23">
-        <v>4</v>
+      <c r="J11" s="28"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="68"/>
+    </row>
+    <row r="12" spans="1:13" ht="18.600000000000001">
+      <c r="A12" s="29">
+        <v>5</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="24"/>
@@ -2246,13 +2262,13 @@
       <c r="H12" s="26"/>
       <c r="I12" s="27"/>
       <c r="J12" s="28"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="67"/>
-    </row>
-    <row r="13" spans="1:13" ht="18.600000000000001">
-      <c r="A13" s="29">
-        <v>5</v>
+      <c r="K12" s="69"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="71"/>
+    </row>
+    <row r="13" spans="1:13" ht="18" customHeight="1">
+      <c r="A13" s="23">
+        <v>6</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="24"/>
@@ -2263,13 +2279,13 @@
       <c r="H13" s="26"/>
       <c r="I13" s="27"/>
       <c r="J13" s="28"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="50"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="49"/>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
       <c r="A14" s="23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="23"/>
       <c r="C14" s="24"/>
@@ -2280,13 +2296,13 @@
       <c r="H14" s="26"/>
       <c r="I14" s="27"/>
       <c r="J14" s="28"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="55"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="68"/>
     </row>
     <row r="15" spans="1:13" ht="18" customHeight="1">
-      <c r="A15" s="23">
-        <v>7</v>
+      <c r="A15" s="22">
+        <v>8</v>
       </c>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -2297,13 +2313,13 @@
       <c r="H15" s="26"/>
       <c r="I15" s="27"/>
       <c r="J15" s="28"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="67"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="71"/>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1">
-      <c r="A16" s="22">
-        <v>8</v>
+      <c r="A16" s="23">
+        <v>9</v>
       </c>
       <c r="B16" s="23"/>
       <c r="C16" s="24"/>
@@ -2314,13 +2330,13 @@
       <c r="H16" s="26"/>
       <c r="I16" s="27"/>
       <c r="J16" s="28"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="50"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="71"/>
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1">
       <c r="A17" s="23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="24"/>
@@ -2331,30 +2347,42 @@
       <c r="H17" s="26"/>
       <c r="I17" s="27"/>
       <c r="J17" s="28"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="50"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="71"/>
     </row>
     <row r="18" spans="1:13" ht="18" customHeight="1">
-      <c r="A18" s="23">
-        <v>10</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="A18" s="29">
+        <v>11</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>31</v>
+      </c>
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="26"/>
+      <c r="H18" s="26">
+        <v>1</v>
+      </c>
       <c r="I18" s="27"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="50"/>
+      <c r="J18" s="28">
+        <v>688</v>
+      </c>
+      <c r="K18" s="69"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="71"/>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1">
-      <c r="A19" s="29">
-        <v>11</v>
+      <c r="A19" s="23">
+        <v>12</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>30</v>
@@ -2363,10 +2391,10 @@
         <v>25</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F19" s="25"/>
       <c r="G19" s="25"/>
@@ -2377,13 +2405,13 @@
       <c r="J19" s="28">
         <v>688</v>
       </c>
-      <c r="K19" s="48"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="50"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="49"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="23">
-        <v>12</v>
+      <c r="A20" s="29">
+        <v>13</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>30</v>
@@ -2406,13 +2434,13 @@
       <c r="J20" s="28">
         <v>688</v>
       </c>
-      <c r="K20" s="53"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="55"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="68"/>
     </row>
     <row r="21" spans="1:13" ht="18" customHeight="1">
-      <c r="A21" s="29">
-        <v>13</v>
+      <c r="A21" s="23">
+        <v>14</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>30</v>
@@ -2435,13 +2463,13 @@
       <c r="J21" s="28">
         <v>688</v>
       </c>
-      <c r="K21" s="65"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="67"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="71"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1">
-      <c r="A22" s="23">
-        <v>14</v>
+      <c r="A22" s="29">
+        <v>15</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>30</v>
@@ -2464,42 +2492,30 @@
       <c r="J22" s="28">
         <v>688</v>
       </c>
-      <c r="K22" s="48"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="50"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="71"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1">
-      <c r="A23" s="29">
-        <v>15</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>28</v>
-      </c>
+      <c r="A23" s="23">
+        <v>16</v>
+      </c>
+      <c r="B23" s="23"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
       <c r="F23" s="25"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="26">
-        <v>1</v>
-      </c>
+      <c r="H23" s="26"/>
       <c r="I23" s="27"/>
-      <c r="J23" s="28">
-        <v>688</v>
-      </c>
-      <c r="K23" s="48"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="50"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="71"/>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1">
-      <c r="A24" s="23">
-        <v>16</v>
+      <c r="A24" s="29">
+        <v>17</v>
       </c>
       <c r="B24" s="23"/>
       <c r="C24" s="24"/>
@@ -2510,13 +2526,13 @@
       <c r="H24" s="26"/>
       <c r="I24" s="27"/>
       <c r="J24" s="28"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="50"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="71"/>
     </row>
     <row r="25" spans="1:13" ht="18" customHeight="1">
-      <c r="A25" s="29">
-        <v>17</v>
+      <c r="A25" s="23">
+        <v>18</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="24"/>
@@ -2527,13 +2543,13 @@
       <c r="H25" s="26"/>
       <c r="I25" s="27"/>
       <c r="J25" s="28"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="50"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="1:13" ht="18" customHeight="1">
-      <c r="A26" s="23">
-        <v>18</v>
+      <c r="A26" s="29">
+        <v>19</v>
       </c>
       <c r="B26" s="23"/>
       <c r="C26" s="24"/>
@@ -2544,13 +2560,13 @@
       <c r="H26" s="26"/>
       <c r="I26" s="27"/>
       <c r="J26" s="28"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="64"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="71"/>
     </row>
     <row r="27" spans="1:13" ht="18" customHeight="1">
-      <c r="A27" s="29">
-        <v>19</v>
+      <c r="A27" s="23">
+        <v>20</v>
       </c>
       <c r="B27" s="23"/>
       <c r="C27" s="24"/>
@@ -2561,13 +2577,15 @@
       <c r="H27" s="26"/>
       <c r="I27" s="27"/>
       <c r="J27" s="28"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="50"/>
+      <c r="K27" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="70"/>
+      <c r="M27" s="71"/>
     </row>
     <row r="28" spans="1:13" ht="18" customHeight="1">
-      <c r="A28" s="23">
-        <v>20</v>
+      <c r="A28" s="29">
+        <v>21</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="24"/>
@@ -2578,15 +2596,15 @@
       <c r="H28" s="26"/>
       <c r="I28" s="27"/>
       <c r="J28" s="28"/>
-      <c r="K28" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" s="49"/>
-      <c r="M28" s="50"/>
+      <c r="K28" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="70"/>
+      <c r="M28" s="71"/>
     </row>
     <row r="29" spans="1:13" ht="18" customHeight="1">
-      <c r="A29" s="29">
-        <v>21</v>
+      <c r="A29" s="23">
+        <v>22</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="24"/>
@@ -2597,15 +2615,15 @@
       <c r="H29" s="26"/>
       <c r="I29" s="27"/>
       <c r="J29" s="28"/>
-      <c r="K29" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="L29" s="49"/>
-      <c r="M29" s="50"/>
+      <c r="K29" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
     </row>
     <row r="30" spans="1:13" ht="18" customHeight="1">
-      <c r="A30" s="23">
-        <v>22</v>
+      <c r="A30" s="29">
+        <v>23</v>
       </c>
       <c r="B30" s="23"/>
       <c r="C30" s="24"/>
@@ -2616,15 +2634,13 @@
       <c r="H30" s="26"/>
       <c r="I30" s="27"/>
       <c r="J30" s="28"/>
-      <c r="K30" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="L30" s="63"/>
-      <c r="M30" s="64"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="71"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1">
-      <c r="A31" s="29">
-        <v>23</v>
+      <c r="A31" s="23">
+        <v>24</v>
       </c>
       <c r="B31" s="23"/>
       <c r="C31" s="24"/>
@@ -2635,13 +2651,13 @@
       <c r="H31" s="26"/>
       <c r="I31" s="27"/>
       <c r="J31" s="28"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="50"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="71"/>
     </row>
     <row r="32" spans="1:13" ht="18" customHeight="1">
-      <c r="A32" s="23">
-        <v>24</v>
+      <c r="A32" s="29">
+        <v>25</v>
       </c>
       <c r="B32" s="23"/>
       <c r="C32" s="24"/>
@@ -2652,13 +2668,13 @@
       <c r="H32" s="26"/>
       <c r="I32" s="27"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="50"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="71"/>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1">
-      <c r="A33" s="29">
-        <v>25</v>
+      <c r="A33" s="23">
+        <v>26</v>
       </c>
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
@@ -2669,13 +2685,13 @@
       <c r="H33" s="26"/>
       <c r="I33" s="27"/>
       <c r="J33" s="28"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="50"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="71"/>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1">
-      <c r="A34" s="23">
-        <v>26</v>
+      <c r="A34" s="29">
+        <v>27</v>
       </c>
       <c r="B34" s="23"/>
       <c r="C34" s="24"/>
@@ -2686,13 +2702,13 @@
       <c r="H34" s="26"/>
       <c r="I34" s="27"/>
       <c r="J34" s="28"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="50"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="71"/>
     </row>
     <row r="35" spans="1:13" ht="18" customHeight="1">
-      <c r="A35" s="29">
-        <v>27</v>
+      <c r="A35" s="23">
+        <v>28</v>
       </c>
       <c r="B35" s="23"/>
       <c r="C35" s="24"/>
@@ -2703,13 +2719,13 @@
       <c r="H35" s="26"/>
       <c r="I35" s="27"/>
       <c r="J35" s="28"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="50"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="49"/>
     </row>
     <row r="36" spans="1:13" ht="18" customHeight="1">
-      <c r="A36" s="23">
-        <v>28</v>
+      <c r="A36" s="29">
+        <v>29</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="24"/>
@@ -2720,13 +2736,13 @@
       <c r="H36" s="26"/>
       <c r="I36" s="27"/>
       <c r="J36" s="28"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="55"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="49"/>
     </row>
     <row r="37" spans="1:13" ht="18" customHeight="1">
-      <c r="A37" s="29">
-        <v>29</v>
+      <c r="A37" s="23">
+        <v>30</v>
       </c>
       <c r="B37" s="23"/>
       <c r="C37" s="24"/>
@@ -2737,14 +2753,12 @@
       <c r="H37" s="26"/>
       <c r="I37" s="27"/>
       <c r="J37" s="28"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="55"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="71"/>
     </row>
     <row r="38" spans="1:13" ht="18" customHeight="1">
-      <c r="A38" s="23">
-        <v>30</v>
-      </c>
+      <c r="A38" s="29"/>
       <c r="B38" s="23"/>
       <c r="C38" s="24"/>
       <c r="D38" s="25"/>
@@ -2754,218 +2768,218 @@
       <c r="H38" s="26"/>
       <c r="I38" s="27"/>
       <c r="J38" s="28"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="50"/>
-    </row>
-    <row r="39" spans="1:13" ht="18" customHeight="1">
-      <c r="A39" s="29"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="48"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="50"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="71"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.6" customHeight="1">
+      <c r="A39" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="23"/>
+      <c r="J39" s="33">
+        <f>(H39*$L$5)+(I39*$L$3)</f>
+        <v>4128</v>
+      </c>
+      <c r="K39" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L39" s="48"/>
+      <c r="M39" s="49"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="51" t="s">
+      <c r="A40" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="25" t="s">
-        <v>36</v>
-      </c>
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="25"/>
       <c r="I40" s="23"/>
       <c r="J40" s="33">
-        <f>(H40*$L$6)+(I40*$L$4)</f>
-        <v>4128</v>
-      </c>
-      <c r="K40" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="L40" s="54"/>
-      <c r="M40" s="55"/>
-    </row>
-    <row r="41" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A41" s="51" t="s">
+        <f>H40*L5</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" s="83"/>
+      <c r="M40" s="84"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A41" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="25"/>
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="32"/>
       <c r="I41" s="23"/>
       <c r="J41" s="33">
-        <f>H41*L6</f>
+        <f>I41*L3</f>
         <v>0</v>
       </c>
-      <c r="K41" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="L41" s="57"/>
-      <c r="M41" s="58"/>
+      <c r="K41" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="48"/>
+      <c r="M41" s="49"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="33">
-        <f>I42*L4</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="54"/>
-      <c r="M42" s="55"/>
-    </row>
-    <row r="43" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A43" s="48" t="str">
-        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J43)&amp;")"</f>
+      <c r="A42" s="69" t="str">
+        <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
         <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
       </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="25" t="s">
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I43" s="31"/>
-      <c r="J43" s="34">
-        <f>SUM(J40:J42)</f>
+      <c r="I42" s="31"/>
+      <c r="J42" s="34">
+        <f>SUM(J39:J41)</f>
         <v>4128</v>
       </c>
-      <c r="K43" s="59" t="s">
+      <c r="K42" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="L43" s="60"/>
-      <c r="M43" s="61"/>
-    </row>
-    <row r="44" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A44" s="45" t="s">
+      <c r="L42" s="64"/>
+      <c r="M42" s="65"/>
+    </row>
+    <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
+      <c r="A43" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="45" t="s">
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="45" t="s">
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="L44" s="46"/>
-      <c r="M44" s="47"/>
-    </row>
-    <row r="45" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A45" s="36"/>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="36"/>
-      <c r="L45" s="37"/>
-      <c r="M45" s="38"/>
-    </row>
-    <row r="46" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A46" s="36" t="s">
+      <c r="L43" s="77"/>
+      <c r="M43" s="78"/>
+    </row>
+    <row r="44" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A44" s="85"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="79"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="44"/>
+      <c r="M44" s="79"/>
+    </row>
+    <row r="45" spans="1:13" ht="17.25" customHeight="1">
+      <c r="A45" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="36" t="s">
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="36" t="s">
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="79"/>
+      <c r="K45" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="L46" s="37"/>
-      <c r="M46" s="38"/>
-    </row>
-    <row r="47" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A47" s="36" t="s">
+      <c r="L45" s="44"/>
+      <c r="M45" s="79"/>
+    </row>
+    <row r="46" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A46" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="36" t="s">
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="39" t="s">
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="L47" s="40"/>
-      <c r="M47" s="41"/>
-    </row>
-    <row r="48" spans="1:13" ht="21" customHeight="1">
-      <c r="A48" s="42" t="s">
+      <c r="L46" s="87"/>
+      <c r="M46" s="88"/>
+    </row>
+    <row r="47" spans="1:13" ht="21" customHeight="1">
+      <c r="A47" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="B48" s="43"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="42" t="s">
+      <c r="B47" s="90"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="91"/>
+      <c r="E47" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="42" t="s">
+      <c r="F47" s="90"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="90"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="L48" s="43"/>
-      <c r="M48" s="44"/>
+      <c r="L47" s="90"/>
+      <c r="M47" s="91"/>
+    </row>
+    <row r="48" spans="1:13" ht="18">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13" ht="18">
       <c r="A49" s="4"/>
@@ -3027,44 +3041,49 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
     </row>
-    <row r="53" spans="1:13" ht="18">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-    </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:J43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="K25:M25"/>
     <mergeCell ref="K14:M14"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="K26:M26"/>
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="K17:M17"/>
@@ -3075,46 +3094,26 @@
     <mergeCell ref="K22:M22"/>
     <mergeCell ref="K23:M23"/>
     <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="K42:M42"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:J48"/>
-    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="L4:M4"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719A5C53-6212-4EC4-94A1-20F514B9F29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E4A0A5-927E-4D94-ACF0-E1FB75DE2889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>(นางสาวอัญญารัตน์ แสงจันทร์)</t>
+  </si>
+  <si>
+    <t>(นายปฐม  ชุมวงศ์)</t>
   </si>
   <si>
     <t>ผู้เบิก</t>
@@ -274,9 +277,6 @@
   </si>
   <si>
     <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
-  </si>
-  <si>
-    <t>(นายปฐม  ชุมวงค์)</t>
   </si>
 </sst>
 </file>
@@ -636,6 +636,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -705,37 +714,55 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -747,7 +774,43 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -786,91 +849,28 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1221,8 +1221,8 @@
     <col min="2" max="2" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.109375" style="2" customWidth="1"/>
     <col min="4" max="7" width="7.6640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" style="2" customWidth="1"/>
     <col min="10" max="10" width="9.109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="4.5546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.88671875" style="1" customWidth="1"/>
@@ -1996,46 +1996,46 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41" t="s">
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="42"/>
+      <c r="M2" s="88"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="43"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="89"/>
       <c r="L3" s="10">
         <v>86</v>
       </c>
@@ -2044,927 +2044,927 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="45" t="s">
+      <c r="A4" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="46"/>
+      <c r="M4" s="91"/>
     </row>
     <row r="5" spans="1:13" ht="20.399999999999999">
       <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="46"/>
+      <c r="D5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="37" t="s">
+      <c r="E5" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="50" t="s">
+      <c r="G5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="50"/>
-      <c r="J5" s="14" t="s">
-        <v>52</v>
+      <c r="I5" s="71"/>
+      <c r="J5" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="18">
         <v>688</v>
       </c>
-      <c r="M5" s="35" t="s">
+      <c r="M5" s="38" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="55" t="s">
+      <c r="K6" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="56"/>
-      <c r="M6" s="57"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="78"/>
     </row>
     <row r="7" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="73"/>
+      <c r="B7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="58" t="s">
+      <c r="C7" s="75"/>
+      <c r="D7" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="58" t="s">
+      <c r="E7" s="80"/>
+      <c r="F7" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="59"/>
-      <c r="H7" s="18" t="s">
+      <c r="G7" s="80"/>
+      <c r="H7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="81" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="82"/>
+      <c r="M7" s="83"/>
+    </row>
+    <row r="8" spans="1:13" ht="18" customHeight="1">
+      <c r="A8" s="25">
+        <v>1</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+    </row>
+    <row r="9" spans="1:13" ht="18" customHeight="1">
+      <c r="A9" s="26">
+        <v>2</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="70"/>
+    </row>
+    <row r="10" spans="1:13" ht="18" customHeight="1">
+      <c r="A10" s="32">
+        <v>3</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="29">
+        <v>1</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="68"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="70"/>
+    </row>
+    <row r="11" spans="1:13" ht="18" customHeight="1">
+      <c r="A11" s="26">
+        <v>4</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="70"/>
+    </row>
+    <row r="12" spans="1:13" ht="18.600000000000001">
+      <c r="A12" s="32">
+        <v>5</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="53"/>
+    </row>
+    <row r="13" spans="1:13" ht="18" customHeight="1">
+      <c r="A13" s="26">
+        <v>6</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="58"/>
+    </row>
+    <row r="14" spans="1:13" ht="18" customHeight="1">
+      <c r="A14" s="26">
+        <v>7</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="70"/>
+    </row>
+    <row r="15" spans="1:13" ht="18" customHeight="1">
+      <c r="A15" s="25">
+        <v>8</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="53"/>
+    </row>
+    <row r="16" spans="1:13" ht="18" customHeight="1">
+      <c r="A16" s="26">
+        <v>9</v>
+      </c>
+      <c r="B16" s="26"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="53"/>
+    </row>
+    <row r="17" spans="1:13" ht="18" customHeight="1">
+      <c r="A17" s="26">
+        <v>10</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="53"/>
+    </row>
+    <row r="18" spans="1:13" ht="18" customHeight="1">
+      <c r="A18" s="32">
+        <v>11</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29">
+        <v>1</v>
+      </c>
+      <c r="I18" s="30"/>
+      <c r="J18" s="31">
+        <v>688</v>
+      </c>
+      <c r="K18" s="51"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="53"/>
+    </row>
+    <row r="19" spans="1:13" ht="18" customHeight="1">
+      <c r="A19" s="26">
+        <v>12</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29">
+        <v>1</v>
+      </c>
+      <c r="I19" s="30"/>
+      <c r="J19" s="31">
+        <v>688</v>
+      </c>
+      <c r="K19" s="56"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
+    </row>
+    <row r="20" spans="1:13" ht="18" customHeight="1">
+      <c r="A20" s="32">
+        <v>13</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29">
+        <v>1</v>
+      </c>
+      <c r="I20" s="30"/>
+      <c r="J20" s="31">
+        <v>688</v>
+      </c>
+      <c r="K20" s="68"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="70"/>
+    </row>
+    <row r="21" spans="1:13" ht="18" customHeight="1">
+      <c r="A21" s="26">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29">
+        <v>1</v>
+      </c>
+      <c r="I21" s="30"/>
+      <c r="J21" s="31">
+        <v>688</v>
+      </c>
+      <c r="K21" s="51"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="53"/>
+    </row>
+    <row r="22" spans="1:13" ht="18" customHeight="1">
+      <c r="A22" s="32">
+        <v>15</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29">
+        <v>1</v>
+      </c>
+      <c r="I22" s="30"/>
+      <c r="J22" s="31">
+        <v>688</v>
+      </c>
+      <c r="K22" s="51"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="53"/>
+    </row>
+    <row r="23" spans="1:13" ht="18" customHeight="1">
+      <c r="A23" s="26">
+        <v>16</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
+    </row>
+    <row r="24" spans="1:13" ht="18" customHeight="1">
+      <c r="A24" s="32">
+        <v>17</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="53"/>
+    </row>
+    <row r="25" spans="1:13" ht="18" customHeight="1">
+      <c r="A25" s="26">
+        <v>18</v>
+      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="67"/>
+    </row>
+    <row r="26" spans="1:13" ht="18" customHeight="1">
+      <c r="A26" s="32">
+        <v>19</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="53"/>
+    </row>
+    <row r="27" spans="1:13" ht="18" customHeight="1">
+      <c r="A27" s="26">
+        <v>20</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
+    </row>
+    <row r="28" spans="1:13" ht="18" customHeight="1">
+      <c r="A28" s="32">
+        <v>21</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="52"/>
+      <c r="M28" s="53"/>
+    </row>
+    <row r="29" spans="1:13" ht="18" customHeight="1">
+      <c r="A29" s="26">
+        <v>22</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="61"/>
-      <c r="M7" s="62"/>
-    </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1">
-      <c r="A8" s="22">
-        <v>1</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="65"/>
-    </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1">
-      <c r="A9" s="23">
-        <v>2</v>
-      </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="66"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="68"/>
-    </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="29">
-        <v>3</v>
-      </c>
-      <c r="B10" s="30" t="s">
+      <c r="L29" s="66"/>
+      <c r="M29" s="67"/>
+    </row>
+    <row r="30" spans="1:13" ht="18" customHeight="1">
+      <c r="A30" s="32">
+        <v>23</v>
+      </c>
+      <c r="B30" s="26"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="53"/>
+    </row>
+    <row r="31" spans="1:13" ht="18" customHeight="1">
+      <c r="A31" s="26">
         <v>24</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="B31" s="26"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="53"/>
+    </row>
+    <row r="32" spans="1:13" ht="18" customHeight="1">
+      <c r="A32" s="32">
         <v>25</v>
       </c>
-      <c r="D10" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="25" t="s">
+      <c r="B32" s="26"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="53"/>
+    </row>
+    <row r="33" spans="1:13" ht="18" customHeight="1">
+      <c r="A33" s="26">
+        <v>26</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="53"/>
+    </row>
+    <row r="34" spans="1:13" ht="18" customHeight="1">
+      <c r="A34" s="32">
         <v>27</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="B34" s="26"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="53"/>
+    </row>
+    <row r="35" spans="1:13" ht="18" customHeight="1">
+      <c r="A35" s="26">
         <v>28</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="58"/>
+    </row>
+    <row r="36" spans="1:13" ht="18" customHeight="1">
+      <c r="A36" s="32">
         <v>29</v>
       </c>
-      <c r="H10" s="26">
-        <v>1</v>
-      </c>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" s="66"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="68"/>
-    </row>
-    <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="23">
-        <v>4</v>
-      </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="67"/>
-      <c r="M11" s="68"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.600000000000001">
-      <c r="A12" s="29">
-        <v>5</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="71"/>
-    </row>
-    <row r="13" spans="1:13" ht="18" customHeight="1">
-      <c r="A13" s="23">
-        <v>6</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="49"/>
-    </row>
-    <row r="14" spans="1:13" ht="18" customHeight="1">
-      <c r="A14" s="23">
-        <v>7</v>
-      </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
-      <c r="M14" s="68"/>
-    </row>
-    <row r="15" spans="1:13" ht="18" customHeight="1">
-      <c r="A15" s="22">
-        <v>8</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="71"/>
-    </row>
-    <row r="16" spans="1:13" ht="18" customHeight="1">
-      <c r="A16" s="23">
-        <v>9</v>
-      </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="71"/>
-    </row>
-    <row r="17" spans="1:13" ht="18" customHeight="1">
-      <c r="A17" s="23">
-        <v>10</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="71"/>
-    </row>
-    <row r="18" spans="1:13" ht="18" customHeight="1">
-      <c r="A18" s="29">
-        <v>11</v>
-      </c>
-      <c r="B18" s="23" t="s">
+      <c r="B36" s="26"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="58"/>
+    </row>
+    <row r="37" spans="1:13" ht="18" customHeight="1">
+      <c r="A37" s="26">
         <v>30</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="26">
-        <v>1</v>
-      </c>
-      <c r="I18" s="27"/>
-      <c r="J18" s="28">
-        <v>688</v>
-      </c>
-      <c r="K18" s="69"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="71"/>
-    </row>
-    <row r="19" spans="1:13" ht="18" customHeight="1">
-      <c r="A19" s="23">
-        <v>12</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26">
-        <v>1</v>
-      </c>
-      <c r="I19" s="27"/>
-      <c r="J19" s="28">
-        <v>688</v>
-      </c>
-      <c r="K19" s="47"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="49"/>
-    </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="29">
-        <v>13</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26">
-        <v>1</v>
-      </c>
-      <c r="I20" s="27"/>
-      <c r="J20" s="28">
-        <v>688</v>
-      </c>
-      <c r="K20" s="66"/>
-      <c r="L20" s="67"/>
-      <c r="M20" s="68"/>
-    </row>
-    <row r="21" spans="1:13" ht="18" customHeight="1">
-      <c r="A21" s="23">
-        <v>14</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26">
-        <v>1</v>
-      </c>
-      <c r="I21" s="27"/>
-      <c r="J21" s="28">
-        <v>688</v>
-      </c>
-      <c r="K21" s="69"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="71"/>
-    </row>
-    <row r="22" spans="1:13" ht="18" customHeight="1">
-      <c r="A22" s="29">
-        <v>15</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26">
-        <v>1</v>
-      </c>
-      <c r="I22" s="27"/>
-      <c r="J22" s="28">
-        <v>688</v>
-      </c>
-      <c r="K22" s="69"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="71"/>
-    </row>
-    <row r="23" spans="1:13" ht="18" customHeight="1">
-      <c r="A23" s="23">
-        <v>16</v>
-      </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="71"/>
-    </row>
-    <row r="24" spans="1:13" ht="18" customHeight="1">
-      <c r="A24" s="29">
-        <v>17</v>
-      </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="71"/>
-    </row>
-    <row r="25" spans="1:13" ht="18" customHeight="1">
-      <c r="A25" s="23">
-        <v>18</v>
-      </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="75"/>
-    </row>
-    <row r="26" spans="1:13" ht="18" customHeight="1">
-      <c r="A26" s="29">
-        <v>19</v>
-      </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="71"/>
-    </row>
-    <row r="27" spans="1:13" ht="18" customHeight="1">
-      <c r="A27" s="23">
-        <v>20</v>
-      </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="70"/>
-      <c r="M27" s="71"/>
-    </row>
-    <row r="28" spans="1:13" ht="18" customHeight="1">
-      <c r="A28" s="29">
-        <v>21</v>
-      </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="L28" s="70"/>
-      <c r="M28" s="71"/>
-    </row>
-    <row r="29" spans="1:13" ht="18" customHeight="1">
-      <c r="A29" s="23">
-        <v>22</v>
-      </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="L29" s="74"/>
-      <c r="M29" s="75"/>
-    </row>
-    <row r="30" spans="1:13" ht="18" customHeight="1">
-      <c r="A30" s="29">
-        <v>23</v>
-      </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="71"/>
-    </row>
-    <row r="31" spans="1:13" ht="18" customHeight="1">
-      <c r="A31" s="23">
-        <v>24</v>
-      </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="71"/>
-    </row>
-    <row r="32" spans="1:13" ht="18" customHeight="1">
-      <c r="A32" s="29">
-        <v>25</v>
-      </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="69"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="71"/>
-    </row>
-    <row r="33" spans="1:13" ht="18" customHeight="1">
-      <c r="A33" s="23">
-        <v>26</v>
-      </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="71"/>
-    </row>
-    <row r="34" spans="1:13" ht="18" customHeight="1">
-      <c r="A34" s="29">
-        <v>27</v>
-      </c>
-      <c r="B34" s="23"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="71"/>
-    </row>
-    <row r="35" spans="1:13" ht="18" customHeight="1">
-      <c r="A35" s="23">
-        <v>28</v>
-      </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="49"/>
-    </row>
-    <row r="36" spans="1:13" ht="18" customHeight="1">
-      <c r="A36" s="29">
-        <v>29</v>
-      </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="49"/>
-    </row>
-    <row r="37" spans="1:13" ht="18" customHeight="1">
-      <c r="A37" s="23">
-        <v>30</v>
-      </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="71"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="53"/>
     </row>
     <row r="38" spans="1:13" ht="18" customHeight="1">
-      <c r="A38" s="29"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="71"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="53"/>
     </row>
     <row r="39" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A39" s="80" t="s">
+      <c r="A39" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="80"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="80"/>
-      <c r="E39" s="81" t="s">
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="25" t="s">
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="I39" s="23"/>
-      <c r="J39" s="33">
+      <c r="I39" s="26"/>
+      <c r="J39" s="36">
         <f>(H39*$L$5)+(I39*$L$3)</f>
         <v>4128</v>
       </c>
-      <c r="K39" s="47" t="s">
+      <c r="K39" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="L39" s="48"/>
-      <c r="M39" s="49"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="58"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="33">
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="36">
         <f>H40*L5</f>
         <v>0</v>
       </c>
-      <c r="K40" s="82" t="s">
-        <v>59</v>
-      </c>
-      <c r="L40" s="83"/>
-      <c r="M40" s="84"/>
+      <c r="K40" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="60"/>
+      <c r="M40" s="61"/>
     </row>
     <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A41" s="80" t="s">
+      <c r="A41" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="80"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="33">
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="36">
         <f>I41*L3</f>
         <v>0</v>
       </c>
-      <c r="K41" s="47" t="s">
+      <c r="K41" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="48"/>
-      <c r="M41" s="49"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="58"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="69" t="str">
+      <c r="A42" s="51" t="str">
         <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
         <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
       </c>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="25" t="s">
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="I42" s="31"/>
-      <c r="J42" s="34">
+      <c r="I42" s="34"/>
+      <c r="J42" s="37">
         <f>SUM(J39:J41)</f>
         <v>4128</v>
       </c>
-      <c r="K42" s="63" t="s">
+      <c r="K42" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="L42" s="64"/>
-      <c r="M42" s="65"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="64"/>
     </row>
     <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A43" s="76" t="s">
+      <c r="A43" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="76" t="s">
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-      <c r="J43" s="79"/>
-      <c r="K43" s="76" t="s">
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="41"/>
+      <c r="K43" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="L43" s="77"/>
-      <c r="M43" s="78"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="50"/>
     </row>
     <row r="44" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A44" s="85"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="85"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="79"/>
-      <c r="K44" s="85"/>
-      <c r="L44" s="44"/>
-      <c r="M44" s="79"/>
+      <c r="A44" s="39"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="40"/>
+      <c r="M44" s="41"/>
     </row>
     <row r="45" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A45" s="85" t="s">
+      <c r="A45" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="L45" s="40"/>
+      <c r="M45" s="41"/>
+    </row>
+    <row r="46" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A46" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="L46" s="43"/>
+      <c r="M46" s="44"/>
+    </row>
+    <row r="47" spans="1:13" ht="21" customHeight="1">
+      <c r="A47" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="47"/>
+      <c r="K47" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="79"/>
-      <c r="K45" s="85" t="s">
-        <v>60</v>
-      </c>
-      <c r="L45" s="44"/>
-      <c r="M45" s="79"/>
-    </row>
-    <row r="46" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A46" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="85" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="79"/>
-      <c r="K46" s="86" t="s">
-        <v>46</v>
-      </c>
-      <c r="L46" s="87"/>
-      <c r="M46" s="88"/>
-    </row>
-    <row r="47" spans="1:13" ht="21" customHeight="1">
-      <c r="A47" s="89" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="90"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="89" t="s">
-        <v>47</v>
-      </c>
-      <c r="F47" s="90"/>
-      <c r="G47" s="90"/>
-      <c r="H47" s="90"/>
-      <c r="I47" s="90"/>
-      <c r="J47" s="91"/>
-      <c r="K47" s="89" t="s">
-        <v>48</v>
-      </c>
-      <c r="L47" s="90"/>
-      <c r="M47" s="91"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="47"/>
     </row>
     <row r="48" spans="1:13" ht="18">
       <c r="A48" s="4"/>
@@ -3043,18 +3043,50 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="E43:J43"/>
     <mergeCell ref="K43:M43"/>
@@ -3070,50 +3102,18 @@
     <mergeCell ref="K41:M41"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="K42:M42"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="K47:M47"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/178 อัพเดท.xlsx
+++ b/178 อัพเดท.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\Downloads\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E4A0A5-927E-4D94-ACF0-E1FB75DE2889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719A5C53-6212-4EC4-94A1-20F514B9F29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3EDCFC2-A5A2-431C-9539-B0288C97800E}"/>
   </bookViews>
@@ -166,9 +166,6 @@
   </si>
   <si>
     <t>(นางสาวอัญญารัตน์ แสงจันทร์)</t>
-  </si>
-  <si>
-    <t>(นายปฐม  ชุมวงศ์)</t>
   </si>
   <si>
     <t>ผู้เบิก</t>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t xml:space="preserve"> [4] ([5]) [6] รวม [17] วัน</t>
+  </si>
+  <si>
+    <t>(นายปฐม  ชุมวงค์)</t>
   </si>
 </sst>
 </file>
@@ -636,15 +636,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -714,55 +705,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -774,43 +747,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -849,28 +786,91 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1221,8 +1221,8 @@
     <col min="2" max="2" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.109375" style="2" customWidth="1"/>
     <col min="4" max="7" width="7.6640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="4.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="5.109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="4.5546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.88671875" style="1" customWidth="1"/>
@@ -1996,46 +1996,46 @@
       <c r="G1" s="9"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="84" t="s">
+      <c r="J1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
     </row>
     <row r="2" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="87" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="88"/>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="89"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="43"/>
       <c r="L3" s="10">
         <v>86</v>
       </c>
@@ -2044,927 +2044,927 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
-      <c r="A4" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="90" t="s">
+      <c r="A4" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="91"/>
+      <c r="M4" s="46"/>
     </row>
     <row r="5" spans="1:13" ht="20.399999999999999">
       <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="72"/>
+      <c r="F5" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="50"/>
+      <c r="J5" s="14" t="s">
         <v>52</v>
-      </c>
-      <c r="H5" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="17" t="s">
-        <v>53</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L5" s="15">
         <v>688</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="M5" s="35" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="76" t="s">
+      <c r="K6" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="77"/>
-      <c r="M6" s="78"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="57"/>
     </row>
     <row r="7" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A7" s="73"/>
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="52"/>
+      <c r="B7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="75"/>
-      <c r="D7" s="79" t="s">
+      <c r="C7" s="54"/>
+      <c r="D7" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="79" t="s">
+      <c r="E7" s="59"/>
+      <c r="F7" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="21" t="s">
+      <c r="G7" s="59"/>
+      <c r="H7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="81" t="s">
+      <c r="K7" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="61"/>
+      <c r="M7" s="62"/>
+    </row>
+    <row r="8" spans="1:13" ht="18" customHeight="1">
+      <c r="A8" s="22">
+        <v>1</v>
+      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="65"/>
+    </row>
+    <row r="9" spans="1:13" ht="18" customHeight="1">
+      <c r="A9" s="23">
+        <v>2</v>
+      </c>
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="68"/>
+    </row>
+    <row r="10" spans="1:13" ht="18" customHeight="1">
+      <c r="A10" s="29">
+        <v>3</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="82"/>
-      <c r="M7" s="83"/>
-    </row>
-    <row r="8" spans="1:13" ht="18" customHeight="1">
-      <c r="A8" s="25">
+      <c r="E10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="26">
         <v>1</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="64"/>
-    </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1">
-      <c r="A9" s="26">
-        <v>2</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="70"/>
-    </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="32">
-        <v>3</v>
-      </c>
-      <c r="B10" s="33" t="s">
+      <c r="I10" s="27"/>
+      <c r="J10" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="66"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="68"/>
+    </row>
+    <row r="11" spans="1:13" ht="18" customHeight="1">
+      <c r="A11" s="23">
+        <v>4</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="68"/>
+    </row>
+    <row r="12" spans="1:13" ht="18.600000000000001">
+      <c r="A12" s="29">
+        <v>5</v>
+      </c>
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="71"/>
+    </row>
+    <row r="13" spans="1:13" ht="18" customHeight="1">
+      <c r="A13" s="23">
+        <v>6</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="49"/>
+    </row>
+    <row r="14" spans="1:13" ht="18" customHeight="1">
+      <c r="A14" s="23">
+        <v>7</v>
+      </c>
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="68"/>
+    </row>
+    <row r="15" spans="1:13" ht="18" customHeight="1">
+      <c r="A15" s="22">
+        <v>8</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="71"/>
+    </row>
+    <row r="16" spans="1:13" ht="18" customHeight="1">
+      <c r="A16" s="23">
+        <v>9</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="71"/>
+    </row>
+    <row r="17" spans="1:13" ht="18" customHeight="1">
+      <c r="A17" s="23">
+        <v>10</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="71"/>
+    </row>
+    <row r="18" spans="1:13" ht="18" customHeight="1">
+      <c r="A18" s="29">
+        <v>11</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26">
+        <v>1</v>
+      </c>
+      <c r="I18" s="27"/>
+      <c r="J18" s="28">
+        <v>688</v>
+      </c>
+      <c r="K18" s="69"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="71"/>
+    </row>
+    <row r="19" spans="1:13" ht="18" customHeight="1">
+      <c r="A19" s="23">
+        <v>12</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="26">
+        <v>1</v>
+      </c>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28">
+        <v>688</v>
+      </c>
+      <c r="K19" s="47"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="49"/>
+    </row>
+    <row r="20" spans="1:13" ht="18" customHeight="1">
+      <c r="A20" s="29">
+        <v>13</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="26">
+        <v>1</v>
+      </c>
+      <c r="I20" s="27"/>
+      <c r="J20" s="28">
+        <v>688</v>
+      </c>
+      <c r="K20" s="66"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="68"/>
+    </row>
+    <row r="21" spans="1:13" ht="18" customHeight="1">
+      <c r="A21" s="23">
+        <v>14</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26">
+        <v>1</v>
+      </c>
+      <c r="I21" s="27"/>
+      <c r="J21" s="28">
+        <v>688</v>
+      </c>
+      <c r="K21" s="69"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="71"/>
+    </row>
+    <row r="22" spans="1:13" ht="18" customHeight="1">
+      <c r="A22" s="29">
+        <v>15</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26">
+        <v>1</v>
+      </c>
+      <c r="I22" s="27"/>
+      <c r="J22" s="28">
+        <v>688</v>
+      </c>
+      <c r="K22" s="69"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="71"/>
+    </row>
+    <row r="23" spans="1:13" ht="18" customHeight="1">
+      <c r="A23" s="23">
+        <v>16</v>
+      </c>
+      <c r="B23" s="23"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="71"/>
+    </row>
+    <row r="24" spans="1:13" ht="18" customHeight="1">
+      <c r="A24" s="29">
+        <v>17</v>
+      </c>
+      <c r="B24" s="23"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="71"/>
+    </row>
+    <row r="25" spans="1:13" ht="18" customHeight="1">
+      <c r="A25" s="23">
+        <v>18</v>
+      </c>
+      <c r="B25" s="23"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="74"/>
+      <c r="M25" s="75"/>
+    </row>
+    <row r="26" spans="1:13" ht="18" customHeight="1">
+      <c r="A26" s="29">
+        <v>19</v>
+      </c>
+      <c r="B26" s="23"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="71"/>
+    </row>
+    <row r="27" spans="1:13" ht="18" customHeight="1">
+      <c r="A27" s="23">
+        <v>20</v>
+      </c>
+      <c r="B27" s="23"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="70"/>
+      <c r="M27" s="71"/>
+    </row>
+    <row r="28" spans="1:13" ht="18" customHeight="1">
+      <c r="A28" s="29">
+        <v>21</v>
+      </c>
+      <c r="B28" s="23"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="70"/>
+      <c r="M28" s="71"/>
+    </row>
+    <row r="29" spans="1:13" ht="18" customHeight="1">
+      <c r="A29" s="23">
+        <v>22</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
+    </row>
+    <row r="30" spans="1:13" ht="18" customHeight="1">
+      <c r="A30" s="29">
+        <v>23</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="71"/>
+    </row>
+    <row r="31" spans="1:13" ht="18" customHeight="1">
+      <c r="A31" s="23">
         <v>24</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="B31" s="23"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="71"/>
+    </row>
+    <row r="32" spans="1:13" ht="18" customHeight="1">
+      <c r="A32" s="29">
         <v>25</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="28" t="s">
+      <c r="B32" s="23"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="71"/>
+    </row>
+    <row r="33" spans="1:13" ht="18" customHeight="1">
+      <c r="A33" s="23">
+        <v>26</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="71"/>
+    </row>
+    <row r="34" spans="1:13" ht="18" customHeight="1">
+      <c r="A34" s="29">
         <v>27</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="B34" s="23"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="71"/>
+    </row>
+    <row r="35" spans="1:13" ht="18" customHeight="1">
+      <c r="A35" s="23">
         <v>28</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="B35" s="23"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="49"/>
+    </row>
+    <row r="36" spans="1:13" ht="18" customHeight="1">
+      <c r="A36" s="29">
         <v>29</v>
       </c>
-      <c r="H10" s="29">
-        <v>1</v>
-      </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="68"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="70"/>
-    </row>
-    <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="26">
-        <v>4</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="70"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.600000000000001">
-      <c r="A12" s="32">
-        <v>5</v>
-      </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="53"/>
-    </row>
-    <row r="13" spans="1:13" ht="18" customHeight="1">
-      <c r="A13" s="26">
-        <v>6</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="58"/>
-    </row>
-    <row r="14" spans="1:13" ht="18" customHeight="1">
-      <c r="A14" s="26">
-        <v>7</v>
-      </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="70"/>
-    </row>
-    <row r="15" spans="1:13" ht="18" customHeight="1">
-      <c r="A15" s="25">
-        <v>8</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="53"/>
-    </row>
-    <row r="16" spans="1:13" ht="18" customHeight="1">
-      <c r="A16" s="26">
-        <v>9</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="53"/>
-    </row>
-    <row r="17" spans="1:13" ht="18" customHeight="1">
-      <c r="A17" s="26">
-        <v>10</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="53"/>
-    </row>
-    <row r="18" spans="1:13" ht="18" customHeight="1">
-      <c r="A18" s="32">
-        <v>11</v>
-      </c>
-      <c r="B18" s="26" t="s">
+      <c r="B36" s="23"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="49"/>
+    </row>
+    <row r="37" spans="1:13" ht="18" customHeight="1">
+      <c r="A37" s="23">
         <v>30</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29">
-        <v>1</v>
-      </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31">
-        <v>688</v>
-      </c>
-      <c r="K18" s="51"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="53"/>
-    </row>
-    <row r="19" spans="1:13" ht="18" customHeight="1">
-      <c r="A19" s="26">
-        <v>12</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29">
-        <v>1</v>
-      </c>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31">
-        <v>688</v>
-      </c>
-      <c r="K19" s="56"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="58"/>
-    </row>
-    <row r="20" spans="1:13" ht="18" customHeight="1">
-      <c r="A20" s="32">
-        <v>13</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29">
-        <v>1</v>
-      </c>
-      <c r="I20" s="30"/>
-      <c r="J20" s="31">
-        <v>688</v>
-      </c>
-      <c r="K20" s="68"/>
-      <c r="L20" s="69"/>
-      <c r="M20" s="70"/>
-    </row>
-    <row r="21" spans="1:13" ht="18" customHeight="1">
-      <c r="A21" s="26">
-        <v>14</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29">
-        <v>1</v>
-      </c>
-      <c r="I21" s="30"/>
-      <c r="J21" s="31">
-        <v>688</v>
-      </c>
-      <c r="K21" s="51"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="53"/>
-    </row>
-    <row r="22" spans="1:13" ht="18" customHeight="1">
-      <c r="A22" s="32">
-        <v>15</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29">
-        <v>1</v>
-      </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="31">
-        <v>688</v>
-      </c>
-      <c r="K22" s="51"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="53"/>
-    </row>
-    <row r="23" spans="1:13" ht="18" customHeight="1">
-      <c r="A23" s="26">
-        <v>16</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="53"/>
-    </row>
-    <row r="24" spans="1:13" ht="18" customHeight="1">
-      <c r="A24" s="32">
-        <v>17</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="53"/>
-    </row>
-    <row r="25" spans="1:13" ht="18" customHeight="1">
-      <c r="A25" s="26">
-        <v>18</v>
-      </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="67"/>
-    </row>
-    <row r="26" spans="1:13" ht="18" customHeight="1">
-      <c r="A26" s="32">
-        <v>19</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="53"/>
-    </row>
-    <row r="27" spans="1:13" ht="18" customHeight="1">
-      <c r="A27" s="26">
-        <v>20</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="52"/>
-      <c r="M27" s="53"/>
-    </row>
-    <row r="28" spans="1:13" ht="18" customHeight="1">
-      <c r="A28" s="32">
-        <v>21</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="L28" s="52"/>
-      <c r="M28" s="53"/>
-    </row>
-    <row r="29" spans="1:13" ht="18" customHeight="1">
-      <c r="A29" s="26">
-        <v>22</v>
-      </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="L29" s="66"/>
-      <c r="M29" s="67"/>
-    </row>
-    <row r="30" spans="1:13" ht="18" customHeight="1">
-      <c r="A30" s="32">
-        <v>23</v>
-      </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="53"/>
-    </row>
-    <row r="31" spans="1:13" ht="18" customHeight="1">
-      <c r="A31" s="26">
-        <v>24</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="53"/>
-    </row>
-    <row r="32" spans="1:13" ht="18" customHeight="1">
-      <c r="A32" s="32">
-        <v>25</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="53"/>
-    </row>
-    <row r="33" spans="1:13" ht="18" customHeight="1">
-      <c r="A33" s="26">
-        <v>26</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="53"/>
-    </row>
-    <row r="34" spans="1:13" ht="18" customHeight="1">
-      <c r="A34" s="32">
-        <v>27</v>
-      </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="51"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="53"/>
-    </row>
-    <row r="35" spans="1:13" ht="18" customHeight="1">
-      <c r="A35" s="26">
-        <v>28</v>
-      </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="58"/>
-    </row>
-    <row r="36" spans="1:13" ht="18" customHeight="1">
-      <c r="A36" s="32">
-        <v>29</v>
-      </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="58"/>
-    </row>
-    <row r="37" spans="1:13" ht="18" customHeight="1">
-      <c r="A37" s="26">
-        <v>30</v>
-      </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="53"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="71"/>
     </row>
     <row r="38" spans="1:13" ht="18" customHeight="1">
-      <c r="A38" s="32"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="53"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="71"/>
     </row>
     <row r="39" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55" t="s">
+      <c r="B39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="28" t="s">
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="36">
+      <c r="I39" s="23"/>
+      <c r="J39" s="33">
         <f>(H39*$L$5)+(I39*$L$3)</f>
         <v>4128</v>
       </c>
-      <c r="K39" s="56" t="s">
+      <c r="K39" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="L39" s="57"/>
-      <c r="M39" s="58"/>
+      <c r="L39" s="48"/>
+      <c r="M39" s="49"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="54"/>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="36">
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="33">
         <f>H40*L5</f>
         <v>0</v>
       </c>
-      <c r="K40" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="L40" s="60"/>
-      <c r="M40" s="61"/>
+      <c r="K40" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" s="83"/>
+      <c r="M40" s="84"/>
     </row>
     <row r="41" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="36">
+      <c r="B41" s="80"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="33">
         <f>I41*L3</f>
         <v>0</v>
       </c>
-      <c r="K41" s="56" t="s">
+      <c r="K41" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="L41" s="57"/>
-      <c r="M41" s="58"/>
+      <c r="L41" s="48"/>
+      <c r="M41" s="49"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A42" s="51" t="str">
+      <c r="A42" s="69" t="str">
         <f xml:space="preserve"> "รวมเงิน ("&amp;BAHTTEXT(J42)&amp;")"</f>
         <v>รวมเงิน (สี่พันหนึ่งร้อยยี่สิบแปดบาทถ้วน)</v>
       </c>
-      <c r="B42" s="52"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="28" t="s">
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I42" s="34"/>
-      <c r="J42" s="37">
+      <c r="I42" s="31"/>
+      <c r="J42" s="34">
         <f>SUM(J39:J41)</f>
         <v>4128</v>
       </c>
-      <c r="K42" s="62" t="s">
+      <c r="K42" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="L42" s="63"/>
-      <c r="M42" s="64"/>
+      <c r="L42" s="64"/>
+      <c r="M42" s="65"/>
     </row>
     <row r="43" spans="1:13" ht="17.399999999999999" customHeight="1" thickTop="1">
-      <c r="A43" s="48" t="s">
+      <c r="A43" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="48" t="s">
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="48" t="s">
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="L43" s="49"/>
-      <c r="M43" s="50"/>
+      <c r="L43" s="77"/>
+      <c r="M43" s="78"/>
     </row>
     <row r="44" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A44" s="39"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="41"/>
+      <c r="A44" s="85"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="79"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="44"/>
+      <c r="M44" s="79"/>
     </row>
     <row r="45" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A45" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="40"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="39" t="s">
+      <c r="A45" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="39" t="s">
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="79"/>
+      <c r="K45" s="85" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" s="44"/>
+      <c r="M45" s="79"/>
+    </row>
+    <row r="46" spans="1:13" ht="19.5" customHeight="1">
+      <c r="A46" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="L45" s="40"/>
-      <c r="M45" s="41"/>
-    </row>
-    <row r="46" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A46" s="39" t="s">
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="39" t="s">
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="79"/>
+      <c r="K46" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="42" t="s">
+      <c r="L46" s="87"/>
+      <c r="M46" s="88"/>
+    </row>
+    <row r="47" spans="1:13" ht="21" customHeight="1">
+      <c r="A47" s="89" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="90"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="91"/>
+      <c r="E47" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="L46" s="43"/>
-      <c r="M46" s="44"/>
-    </row>
-    <row r="47" spans="1:13" ht="21" customHeight="1">
-      <c r="A47" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="45" t="s">
+      <c r="F47" s="90"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="90"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="L47" s="46"/>
-      <c r="M47" s="47"/>
+      <c r="L47" s="90"/>
+      <c r="M47" s="91"/>
     </row>
     <row r="48" spans="1:13" ht="18">
       <c r="A48" s="4"/>
@@ -3043,50 +3043,18 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="K45:M45"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="E43:J43"/>
     <mergeCell ref="K43:M43"/>
@@ -3102,18 +3070,50 @@
     <mergeCell ref="K41:M41"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="K42:M42"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="L4:M4"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
